--- a/chamcong.xlsx
+++ b/chamcong.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ms Phuong\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmcvnpt-my.sharepoint.com/personal/phuongvl_vpc_vnpt_vn/Documents/AI/1chamcong/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8042E9A-3F5C-4731-9B41-1212C11F6FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{A8042E9A-3F5C-4731-9B41-1212C11F6FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{973A4DF6-51BC-464A-9701-273F1E1728F1}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamcong" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6417" uniqueCount="1165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6387" uniqueCount="1145">
   <si>
     <t>TT</t>
   </si>
@@ -1810,70 +1810,10 @@
     <t>Đi làm</t>
   </si>
   <si>
-    <t>X/F</t>
-  </si>
-  <si>
-    <t>Nghỉ phép buổi chiều</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>Nghỉ cưới hỏi</t>
-  </si>
-  <si>
     <t>Việc riêng không lương</t>
   </si>
   <si>
-    <t>RN</t>
-  </si>
-  <si>
-    <t>Ra ngoài việc công ty</t>
-  </si>
-  <si>
-    <t>F/X</t>
-  </si>
-  <si>
-    <t>Nghỉ phép buổi sáng</t>
-  </si>
-  <si>
-    <t>Le</t>
-  </si>
-  <si>
-    <t>Nghỉ lễ</t>
-  </si>
-  <si>
     <t>Phép năm</t>
-  </si>
-  <si>
-    <t>Rv</t>
-  </si>
-  <si>
-    <t>Nghỉ vô kỉ luật, không xin phép</t>
-  </si>
-  <si>
-    <t>X2</t>
-  </si>
-  <si>
-    <t>Đi làm 7h</t>
-  </si>
-  <si>
-    <t>X3</t>
-  </si>
-  <si>
-    <t>Đi làm 9h</t>
-  </si>
-  <si>
-    <t>X4</t>
-  </si>
-  <si>
-    <t>Đi làm 10h</t>
-  </si>
-  <si>
-    <t>TC</t>
-  </si>
-  <si>
-    <t>Ca tăng cường</t>
   </si>
   <si>
     <t>Nghỉ bù</t>
@@ -4099,16 +4039,16 @@
   <sheetData>
     <row r="1" spans="1:35" ht="28" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>908</v>
+        <v>888</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>909</v>
+        <v>889</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>910</v>
+        <v>890</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>911</v>
+        <v>891</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -21176,7 +21116,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6080A41B-F989-4DD2-B967-3264220228D5}">
-  <dimension ref="A1:C168"/>
+  <dimension ref="A1:C158"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="21.08984375" customWidth="1"/>
@@ -21204,287 +21144,287 @@
         <v>589</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="56" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="28" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>592</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="56" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="42" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="42" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="42" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="C7" s="3" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="42" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="C9" s="3" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="42" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C9" s="3" t="s">
+    <row r="11" spans="1:3" ht="42" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="56" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="C11" s="3" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="42" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C12" s="3" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="42" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="28" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>608</v>
-      </c>
       <c r="C13" s="3" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>84</v>
+        <v>606</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="126" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="126" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="126" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="C18" s="3" t="s">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="126" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="112" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
+    </row>
+    <row r="22" spans="1:3" ht="42" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>619</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="112" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="112" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>622</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="112" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="42" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="C24" s="3" t="s">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>625</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="28" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="C25" s="3" t="s">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="56" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
+      <c r="C26" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="C26" s="3" t="s">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>629</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="28" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="3" t="s">
         <v>630</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>43</v>
+        <v>631</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>632</v>
@@ -21492,7 +21432,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>28</v>
+        <v>115</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>633</v>
@@ -21503,7 +21443,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>29</v>
+        <v>118</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>635</v>
@@ -21514,7 +21454,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>30</v>
+        <v>121</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>637</v>
@@ -21523,9 +21463,9 @@
         <v>638</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="126" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>31</v>
+        <v>125</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>639</v>
@@ -21534,9 +21474,9 @@
         <v>640</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>641</v>
@@ -21547,7 +21487,7 @@
     </row>
     <row r="34" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>643</v>
@@ -21558,7 +21498,7 @@
     </row>
     <row r="35" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>645</v>
@@ -21569,7 +21509,7 @@
     </row>
     <row r="36" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>647</v>
@@ -21580,7 +21520,7 @@
     </row>
     <row r="37" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>649</v>
@@ -21591,7 +21531,7 @@
     </row>
     <row r="38" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>651</v>
@@ -21602,7 +21542,7 @@
     </row>
     <row r="39" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>653</v>
@@ -21613,7 +21553,7 @@
     </row>
     <row r="40" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>655</v>
@@ -21624,7 +21564,7 @@
     </row>
     <row r="41" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>657</v>
@@ -21633,9 +21573,9 @@
         <v>658</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>659</v>
@@ -21644,9 +21584,9 @@
         <v>660</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>661</v>
@@ -21655,9 +21595,9 @@
         <v>662</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="56" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>663</v>
@@ -21666,9 +21606,9 @@
         <v>664</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="56" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>665</v>
@@ -21677,9 +21617,9 @@
         <v>666</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="56" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>667</v>
@@ -21688,9 +21628,9 @@
         <v>668</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="56" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>669</v>
@@ -21699,9 +21639,9 @@
         <v>670</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="56" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>671</v>
@@ -21710,9 +21650,9 @@
         <v>672</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="56" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>673</v>
@@ -21721,9 +21661,9 @@
         <v>674</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="56" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>675</v>
@@ -21732,9 +21672,9 @@
         <v>676</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="56" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>677</v>
@@ -21743,141 +21683,141 @@
         <v>678</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="42" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>679</v>
       </c>
       <c r="C52" s="3" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" ht="56" x14ac:dyDescent="0.35">
-      <c r="A53" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B53" s="2" t="s">
+      <c r="C53" s="3" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="84" x14ac:dyDescent="0.35">
-      <c r="A54" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B54" s="2" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="28" x14ac:dyDescent="0.35">
-      <c r="A55" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B55" s="2" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="98" x14ac:dyDescent="0.35">
-      <c r="A56" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B56" s="2" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="56" x14ac:dyDescent="0.35">
-      <c r="A57" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B57" s="2" t="s">
+    <row r="58" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+      <c r="A58" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="56" x14ac:dyDescent="0.35">
-      <c r="A58" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B58" s="2" t="s">
+    <row r="59" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+      <c r="A59" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>692</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="70" x14ac:dyDescent="0.35">
-      <c r="A59" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+      <c r="A61" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="42" x14ac:dyDescent="0.35">
-      <c r="A61" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B61" s="2" t="s">
+    <row r="62" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+      <c r="A62" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B62" s="2" t="s">
+    <row r="63" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+      <c r="A63" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B63" s="2" t="s">
+      <c r="C63" s="3" t="s">
         <v>700</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>701</v>
@@ -21888,7 +21828,7 @@
     </row>
     <row r="65" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>703</v>
@@ -21899,7 +21839,7 @@
     </row>
     <row r="66" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>705</v>
@@ -21908,9 +21848,9 @@
         <v>706</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>707</v>
@@ -21919,9 +21859,9 @@
         <v>708</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>709</v>
@@ -21930,9 +21870,9 @@
         <v>710</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>711</v>
@@ -21941,9 +21881,9 @@
         <v>712</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>713</v>
@@ -21952,9 +21892,9 @@
         <v>714</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>213</v>
+        <v>243</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>715</v>
@@ -21963,9 +21903,9 @@
         <v>716</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>717</v>
@@ -21974,9 +21914,9 @@
         <v>718</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>719</v>
@@ -21985,9 +21925,9 @@
         <v>720</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>721</v>
@@ -21996,9 +21936,9 @@
         <v>722</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>723</v>
@@ -22007,9 +21947,9 @@
         <v>724</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>725</v>
@@ -22018,9 +21958,9 @@
         <v>726</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>727</v>
@@ -22029,9 +21969,9 @@
         <v>728</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" ht="42" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>729</v>
@@ -22040,9 +21980,9 @@
         <v>730</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" ht="56" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>731</v>
@@ -22051,9 +21991,9 @@
         <v>732</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>733</v>
@@ -22062,9 +22002,9 @@
         <v>734</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>735</v>
@@ -22073,9 +22013,9 @@
         <v>736</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>737</v>
@@ -22084,9 +22024,9 @@
         <v>738</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>739</v>
@@ -22095,9 +22035,9 @@
         <v>740</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>741</v>
@@ -22106,9 +22046,9 @@
         <v>742</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>743</v>
@@ -22117,9 +22057,9 @@
         <v>744</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>745</v>
@@ -22128,9 +22068,9 @@
         <v>746</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="56" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>747</v>
@@ -22139,9 +22079,9 @@
         <v>748</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="98" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>749</v>
@@ -22150,9 +22090,9 @@
         <v>750</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="140" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>751</v>
@@ -22161,9 +22101,9 @@
         <v>752</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>753</v>
@@ -22172,9 +22112,9 @@
         <v>754</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>755</v>
@@ -22183,9 +22123,9 @@
         <v>756</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>757</v>
@@ -22194,9 +22134,9 @@
         <v>758</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>759</v>
@@ -22205,9 +22145,9 @@
         <v>760</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>282</v>
+        <v>312</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>761</v>
@@ -22216,9 +22156,9 @@
         <v>762</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>285</v>
+        <v>315</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>763</v>
@@ -22227,9 +22167,9 @@
         <v>764</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>288</v>
+        <v>318</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>765</v>
@@ -22238,9 +22178,9 @@
         <v>766</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>767</v>
@@ -22249,9 +22189,9 @@
         <v>768</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>294</v>
+        <v>324</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>769</v>
@@ -22260,9 +22200,9 @@
         <v>770</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>297</v>
+        <v>327</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>771</v>
@@ -22271,9 +22211,9 @@
         <v>772</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>773</v>
@@ -22282,9 +22222,9 @@
         <v>774</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>775</v>
@@ -22293,9 +22233,9 @@
         <v>776</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>306</v>
+        <v>336</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>777</v>
@@ -22304,9 +22244,9 @@
         <v>778</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>309</v>
+        <v>339</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>779</v>
@@ -22315,9 +22255,9 @@
         <v>780</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>781</v>
@@ -22326,9 +22266,9 @@
         <v>782</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>783</v>
@@ -22337,9 +22277,9 @@
         <v>784</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>318</v>
+        <v>348</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>785</v>
@@ -22348,9 +22288,9 @@
         <v>786</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>787</v>
@@ -22359,9 +22299,9 @@
         <v>788</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>789</v>
@@ -22370,9 +22310,9 @@
         <v>790</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>791</v>
@@ -22381,9 +22321,9 @@
         <v>792</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>793</v>
@@ -22392,9 +22332,9 @@
         <v>794</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>333</v>
+        <v>363</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>795</v>
@@ -22403,9 +22343,9 @@
         <v>796</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>797</v>
@@ -22414,9 +22354,9 @@
         <v>798</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>339</v>
+        <v>368</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>799</v>
@@ -22425,9 +22365,9 @@
         <v>800</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>801</v>
@@ -22436,9 +22376,9 @@
         <v>802</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>345</v>
+        <v>375</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>803</v>
@@ -22447,9 +22387,9 @@
         <v>804</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>348</v>
+        <v>378</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>805</v>
@@ -22458,9 +22398,9 @@
         <v>806</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>807</v>
@@ -22469,9 +22409,9 @@
         <v>808</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>809</v>
@@ -22480,9 +22420,9 @@
         <v>810</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>357</v>
+        <v>387</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>811</v>
@@ -22491,9 +22431,9 @@
         <v>812</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>813</v>
@@ -22502,9 +22442,9 @@
         <v>814</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>815</v>
@@ -22513,9 +22453,9 @@
         <v>816</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
-        <v>366</v>
+        <v>396</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>817</v>
@@ -22524,9 +22464,9 @@
         <v>818</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
-        <v>368</v>
+        <v>399</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>819</v>
@@ -22535,9 +22475,9 @@
         <v>820</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>821</v>
@@ -22546,9 +22486,9 @@
         <v>822</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="84" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
-        <v>375</v>
+        <v>405</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>823</v>
@@ -22557,9 +22497,9 @@
         <v>824</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="56" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
-        <v>378</v>
+        <v>408</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>825</v>
@@ -22568,9 +22508,9 @@
         <v>826</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>827</v>
@@ -22579,9 +22519,9 @@
         <v>828</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
-        <v>384</v>
+        <v>414</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>829</v>
@@ -22590,9 +22530,9 @@
         <v>830</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
-        <v>387</v>
+        <v>417</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>831</v>
@@ -22601,9 +22541,9 @@
         <v>832</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>833</v>
@@ -22612,9 +22552,9 @@
         <v>834</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
-        <v>393</v>
+        <v>423</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>835</v>
@@ -22625,7 +22565,7 @@
     </row>
     <row r="132" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>837</v>
@@ -22636,7 +22576,7 @@
     </row>
     <row r="133" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>839</v>
@@ -22647,7 +22587,7 @@
     </row>
     <row r="134" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
-        <v>402</v>
+        <v>432</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>841</v>
@@ -22656,9 +22596,9 @@
         <v>842</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
-        <v>405</v>
+        <v>435</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>843</v>
@@ -22667,9 +22607,9 @@
         <v>844</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
-        <v>408</v>
+        <v>438</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>845</v>
@@ -22680,7 +22620,7 @@
     </row>
     <row r="137" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
-        <v>411</v>
+        <v>441</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>847</v>
@@ -22689,9 +22629,9 @@
         <v>848</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
-        <v>414</v>
+        <v>444</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>849</v>
@@ -22700,9 +22640,9 @@
         <v>850</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
-        <v>417</v>
+        <v>447</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>851</v>
@@ -22711,9 +22651,9 @@
         <v>852</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>853</v>
@@ -22722,9 +22662,9 @@
         <v>854</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
-        <v>423</v>
+        <v>453</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>855</v>
@@ -22733,9 +22673,9 @@
         <v>856</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
-        <v>426</v>
+        <v>456</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>857</v>
@@ -22744,290 +22684,180 @@
         <v>858</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="70" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
-        <v>429</v>
+        <v>459</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>859</v>
       </c>
       <c r="C143" s="3" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A144" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B144" s="2" t="s">
         <v>860</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" ht="70" x14ac:dyDescent="0.35">
-      <c r="A144" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>861</v>
-      </c>
       <c r="C144" s="3" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="42" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
-        <v>435</v>
+        <v>465</v>
       </c>
       <c r="B145" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A146" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B146" s="2" t="s">
         <v>863</v>
       </c>
-      <c r="C145" s="3" t="s">
+      <c r="C146" s="3" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="42" x14ac:dyDescent="0.35">
-      <c r="A146" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="B146" s="2" t="s">
+    <row r="147" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+      <c r="A147" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>865</v>
       </c>
-      <c r="C146" s="3" t="s">
+      <c r="C147" s="3" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="42" x14ac:dyDescent="0.35">
-      <c r="A147" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="B147" s="2" t="s">
+    <row r="148" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+      <c r="A148" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B148" s="2" t="s">
         <v>867</v>
       </c>
-      <c r="C147" s="3" t="s">
+      <c r="C148" s="3" t="s">
         <v>868</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" ht="56" x14ac:dyDescent="0.35">
-      <c r="A148" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>869</v>
-      </c>
-      <c r="C148" s="3" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
-        <v>447</v>
+        <v>477</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="B150" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A151" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>873</v>
       </c>
-      <c r="C150" s="3" t="s">
+      <c r="C151" s="3" t="s">
         <v>874</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" ht="56" x14ac:dyDescent="0.35">
-      <c r="A151" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>875</v>
-      </c>
-      <c r="C151" s="3" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
-        <v>456</v>
+        <v>486</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>877</v>
+        <v>374</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
-        <v>459</v>
+        <v>489</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
-        <v>462</v>
+        <v>492</v>
       </c>
       <c r="B154" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A155" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B155" s="2" t="s">
         <v>880</v>
       </c>
-      <c r="C154" s="3" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" ht="98" x14ac:dyDescent="0.35">
-      <c r="A155" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="B155" s="2" t="s">
+      <c r="C155" s="3" t="s">
         <v>881</v>
       </c>
-      <c r="C155" s="3" t="s">
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A156" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B156" s="2" t="s">
         <v>882</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" ht="56" x14ac:dyDescent="0.35">
-      <c r="A156" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="B156" s="2" t="s">
+      <c r="C156" s="3" t="s">
         <v>883</v>
       </c>
-      <c r="C156" s="3" t="s">
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A157" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B157" s="2" t="s">
         <v>884</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" ht="84" x14ac:dyDescent="0.35">
-      <c r="A157" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="B157" s="2" t="s">
+      <c r="C157" s="3" t="s">
         <v>885</v>
       </c>
-      <c r="C157" s="3" t="s">
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A158" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B158" s="2" t="s">
         <v>886</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" ht="56" x14ac:dyDescent="0.35">
-      <c r="A158" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="B158" s="2" t="s">
+      <c r="C158" s="3" t="s">
         <v>887</v>
-      </c>
-      <c r="C158" s="3" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" ht="84" x14ac:dyDescent="0.35">
-      <c r="A159" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>889</v>
-      </c>
-      <c r="C159" s="3" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" ht="42" x14ac:dyDescent="0.35">
-      <c r="A160" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A161" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>893</v>
-      </c>
-      <c r="C161" s="3" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A162" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C162" s="3" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" ht="28" x14ac:dyDescent="0.35">
-      <c r="A163" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="C163" s="3" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A164" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>898</v>
-      </c>
-      <c r="C164" s="3" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" ht="42" x14ac:dyDescent="0.35">
-      <c r="A165" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>900</v>
-      </c>
-      <c r="C165" s="3" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" ht="42" x14ac:dyDescent="0.35">
-      <c r="A166" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>902</v>
-      </c>
-      <c r="C166" s="3" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" ht="42" x14ac:dyDescent="0.35">
-      <c r="A167" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>904</v>
-      </c>
-      <c r="C167" s="3" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" ht="28" x14ac:dyDescent="0.35">
-      <c r="A168" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>906</v>
-      </c>
-      <c r="C168" s="3" t="s">
-        <v>907</v>
       </c>
     </row>
   </sheetData>
@@ -23045,28 +22875,28 @@
   <sheetData>
     <row r="1" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>908</v>
+        <v>888</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>912</v>
+        <v>892</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>913</v>
+        <v>893</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>914</v>
+        <v>894</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>915</v>
+        <v>895</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>916</v>
+        <v>896</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>917</v>
+        <v>897</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>918</v>
+        <v>898</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -23084,7 +22914,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>919</v>
+        <v>899</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>32</v>
@@ -23096,10 +22926,10 @@
         <v>29698</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>920</v>
+        <v>900</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>921</v>
+        <v>901</v>
       </c>
       <c r="H3" s="7">
         <v>912222493</v>
@@ -23110,7 +22940,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>919</v>
+        <v>899</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>35</v>
@@ -23122,10 +22952,10 @@
         <v>30356</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>922</v>
+        <v>902</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>923</v>
+        <v>903</v>
       </c>
       <c r="H4" s="7">
         <v>913282346</v>
@@ -23136,7 +22966,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>919</v>
+        <v>899</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>37</v>
@@ -23148,10 +22978,10 @@
         <v>27992</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>922</v>
+        <v>902</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>924</v>
+        <v>904</v>
       </c>
       <c r="H5" s="7">
         <v>912026525</v>
@@ -23162,7 +22992,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>82</v>
@@ -23174,10 +23004,10 @@
         <v>29928</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>926</v>
+        <v>906</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>927</v>
+        <v>907</v>
       </c>
       <c r="H6" s="7">
         <v>915225103</v>
@@ -23188,7 +23018,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>85</v>
@@ -23200,10 +23030,10 @@
         <v>27060</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>929</v>
+        <v>909</v>
       </c>
       <c r="H7" s="7">
         <v>912664497</v>
@@ -23214,7 +23044,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>87</v>
@@ -23226,10 +23056,10 @@
         <v>29397</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="H8" s="7">
         <v>912550789</v>
@@ -23240,7 +23070,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>89</v>
@@ -23252,10 +23082,10 @@
         <v>28689</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>926</v>
+        <v>906</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>931</v>
+        <v>911</v>
       </c>
       <c r="H9" s="7">
         <v>916167717</v>
@@ -23266,7 +23096,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>91</v>
@@ -23278,10 +23108,10 @@
         <v>32221</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>932</v>
+        <v>912</v>
       </c>
       <c r="H10" s="7">
         <v>917238588</v>
@@ -23292,7 +23122,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>93</v>
@@ -23304,10 +23134,10 @@
         <v>28546</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>933</v>
+        <v>913</v>
       </c>
       <c r="H11" s="7">
         <v>912247005</v>
@@ -23318,7 +23148,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>95</v>
@@ -23330,10 +23160,10 @@
         <v>28421</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>934</v>
+        <v>914</v>
       </c>
       <c r="H12" s="7">
         <v>813697799</v>
@@ -23344,7 +23174,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>98</v>
@@ -23356,10 +23186,10 @@
         <v>31293</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>935</v>
+        <v>915</v>
       </c>
       <c r="H13" s="7">
         <v>946066699</v>
@@ -23370,7 +23200,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>101</v>
@@ -23382,10 +23212,10 @@
         <v>30032</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>936</v>
+        <v>916</v>
       </c>
       <c r="H14" s="7">
         <v>919782286</v>
@@ -23396,7 +23226,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>104</v>
@@ -23408,10 +23238,10 @@
         <v>30948</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>937</v>
+        <v>917</v>
       </c>
       <c r="H15" s="7">
         <v>915773888</v>
@@ -23422,7 +23252,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>107</v>
@@ -23434,10 +23264,10 @@
         <v>30401</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>938</v>
+        <v>918</v>
       </c>
       <c r="H16" s="7">
         <v>915030165</v>
@@ -23448,7 +23278,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>110</v>
@@ -23460,10 +23290,10 @@
         <v>32479</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>939</v>
+        <v>919</v>
       </c>
       <c r="H17" s="7">
         <v>912640246</v>
@@ -23474,7 +23304,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>113</v>
@@ -23486,10 +23316,10 @@
         <v>31367</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>940</v>
+        <v>920</v>
       </c>
       <c r="H18" s="7">
         <v>941125125</v>
@@ -23500,7 +23330,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>116</v>
@@ -23512,10 +23342,10 @@
         <v>27629</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>941</v>
+        <v>921</v>
       </c>
       <c r="H19" s="7">
         <v>912259244</v>
@@ -23526,7 +23356,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>119</v>
@@ -23538,10 +23368,10 @@
         <v>33166</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>942</v>
+        <v>922</v>
       </c>
       <c r="H20" s="7">
         <v>911639191</v>
@@ -23552,7 +23382,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>122</v>
@@ -23564,10 +23394,10 @@
         <v>32119</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>943</v>
+        <v>923</v>
       </c>
       <c r="H21" s="7">
         <v>911111987</v>
@@ -23578,7 +23408,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>126</v>
@@ -23590,10 +23420,10 @@
         <v>27021</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>944</v>
+        <v>924</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>945</v>
+        <v>925</v>
       </c>
       <c r="H22" s="7">
         <v>913261808</v>
@@ -23604,7 +23434,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>946</v>
+        <v>926</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>141</v>
@@ -23616,10 +23446,10 @@
         <v>28126</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>947</v>
+        <v>927</v>
       </c>
       <c r="H23" s="7">
         <v>917035444</v>
@@ -23630,7 +23460,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>946</v>
+        <v>926</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>144</v>
@@ -23642,10 +23472,10 @@
         <v>32953</v>
       </c>
       <c r="F24" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>928</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>948</v>
       </c>
       <c r="H24" s="7">
         <v>911232324</v>
@@ -23656,7 +23486,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>946</v>
+        <v>926</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>148</v>
@@ -23668,10 +23498,10 @@
         <v>27669</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>949</v>
+        <v>929</v>
       </c>
       <c r="H25" s="7">
         <v>918153188</v>
@@ -23682,7 +23512,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>946</v>
+        <v>926</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>151</v>
@@ -23694,10 +23524,10 @@
         <v>26388</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>944</v>
+        <v>924</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>950</v>
+        <v>930</v>
       </c>
       <c r="H26" s="7">
         <v>916167929</v>
@@ -23708,7 +23538,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>951</v>
+        <v>931</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>166</v>
@@ -23720,10 +23550,10 @@
         <v>26782</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>926</v>
+        <v>906</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>952</v>
+        <v>932</v>
       </c>
       <c r="H27" s="7">
         <v>912338586</v>
@@ -23734,7 +23564,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>951</v>
+        <v>931</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>169</v>
@@ -23746,10 +23576,10 @@
         <v>27985</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>953</v>
+        <v>933</v>
       </c>
       <c r="H28" s="7">
         <v>912110176</v>
@@ -23760,7 +23590,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>951</v>
+        <v>931</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>172</v>
@@ -23772,10 +23602,10 @@
         <v>33713</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>954</v>
+        <v>934</v>
       </c>
       <c r="H29" s="7">
         <v>911122338</v>
@@ -23786,7 +23616,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>951</v>
+        <v>931</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>175</v>
@@ -23798,10 +23628,10 @@
         <v>31967</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>955</v>
+        <v>935</v>
       </c>
       <c r="H30" s="7">
         <v>915047773</v>
@@ -23812,7 +23642,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>951</v>
+        <v>931</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>178</v>
@@ -23824,10 +23654,10 @@
         <v>27880</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>956</v>
+        <v>936</v>
       </c>
       <c r="H31" s="7">
         <v>915773848</v>
@@ -23838,7 +23668,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>951</v>
+        <v>931</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>181</v>
@@ -23850,10 +23680,10 @@
         <v>29389</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>944</v>
+        <v>924</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>957</v>
+        <v>937</v>
       </c>
       <c r="H32" s="7">
         <v>913170680</v>
@@ -23864,7 +23694,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>951</v>
+        <v>931</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>184</v>
@@ -23876,10 +23706,10 @@
         <v>27581</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>944</v>
+        <v>924</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>958</v>
+        <v>938</v>
       </c>
       <c r="H33" s="7">
         <v>917968768</v>
@@ -23890,7 +23720,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>202</v>
@@ -23902,10 +23732,10 @@
         <v>31560</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>961</v>
+        <v>941</v>
       </c>
       <c r="H34" s="7">
         <v>917161767</v>
@@ -23916,7 +23746,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>205</v>
@@ -23928,10 +23758,10 @@
         <v>33130</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>962</v>
+        <v>942</v>
       </c>
       <c r="H35" s="7">
         <v>916867200</v>
@@ -23942,7 +23772,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>208</v>
@@ -23954,10 +23784,10 @@
         <v>29048</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>963</v>
+        <v>943</v>
       </c>
       <c r="H36" s="7">
         <v>912913305</v>
@@ -23968,7 +23798,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>211</v>
@@ -23980,10 +23810,10 @@
         <v>26750</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>964</v>
+        <v>944</v>
       </c>
       <c r="H37" s="7">
         <v>836569888</v>
@@ -23994,7 +23824,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>214</v>
@@ -24006,10 +23836,10 @@
         <v>32282</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>965</v>
+        <v>945</v>
       </c>
       <c r="H38" s="7">
         <v>918701988</v>
@@ -24020,7 +23850,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>217</v>
@@ -24032,10 +23862,10 @@
         <v>30895</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>966</v>
+        <v>946</v>
       </c>
       <c r="H39" s="7">
         <v>912465450</v>
@@ -24046,7 +23876,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>220</v>
@@ -24058,10 +23888,10 @@
         <v>31280</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>967</v>
+        <v>947</v>
       </c>
       <c r="H40" s="7">
         <v>946221885</v>
@@ -24072,7 +23902,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>223</v>
@@ -24084,10 +23914,10 @@
         <v>29888</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>944</v>
+        <v>924</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>968</v>
+        <v>948</v>
       </c>
       <c r="H41" s="7">
         <v>913096338</v>
@@ -24098,7 +23928,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>262</v>
@@ -24110,10 +23940,10 @@
         <v>26924</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>926</v>
+        <v>906</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="H42" s="7">
         <v>918551138</v>
@@ -24124,7 +23954,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>265</v>
@@ -24136,10 +23966,10 @@
         <v>27361</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>971</v>
+        <v>951</v>
       </c>
       <c r="H43" s="7">
         <v>917867966</v>
@@ -24150,7 +23980,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>268</v>
@@ -24162,10 +23992,10 @@
         <v>32013</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>972</v>
+        <v>952</v>
       </c>
       <c r="H44" s="7">
         <v>946044333</v>
@@ -24176,7 +24006,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>271</v>
@@ -24188,10 +24018,10 @@
         <v>29646</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>926</v>
+        <v>906</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>973</v>
+        <v>953</v>
       </c>
       <c r="H45" s="7">
         <v>948313222</v>
@@ -24202,7 +24032,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>274</v>
@@ -24214,10 +24044,10 @@
         <v>29435</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>926</v>
+        <v>906</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>974</v>
+        <v>954</v>
       </c>
       <c r="H46" s="7">
         <v>913338091</v>
@@ -24228,7 +24058,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>277</v>
@@ -24240,10 +24070,10 @@
         <v>30415</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>944</v>
+        <v>924</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>975</v>
+        <v>955</v>
       </c>
       <c r="H47" s="7">
         <v>912188383</v>
@@ -24254,7 +24084,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>976</v>
+        <v>956</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>292</v>
@@ -24266,10 +24096,10 @@
         <v>27020</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>977</v>
+        <v>957</v>
       </c>
       <c r="H48" s="7">
         <v>915275186</v>
@@ -24280,7 +24110,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>976</v>
+        <v>956</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>295</v>
@@ -24292,10 +24122,10 @@
         <v>31554</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>978</v>
+        <v>958</v>
       </c>
       <c r="H49" s="7">
         <v>915921123</v>
@@ -24306,7 +24136,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>976</v>
+        <v>956</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>298</v>
@@ -24318,10 +24148,10 @@
         <v>30318</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>979</v>
+        <v>959</v>
       </c>
       <c r="H50" s="7">
         <v>838343366</v>
@@ -24332,7 +24162,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>976</v>
+        <v>956</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>301</v>
@@ -24344,10 +24174,10 @@
         <v>26600</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>980</v>
+        <v>960</v>
       </c>
       <c r="H51" s="7">
         <v>912957533</v>
@@ -24358,7 +24188,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>976</v>
+        <v>956</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>304</v>
@@ -24370,10 +24200,10 @@
         <v>29792</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>981</v>
+        <v>961</v>
       </c>
       <c r="H52" s="7">
         <v>916085707</v>
@@ -24384,7 +24214,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>976</v>
+        <v>956</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>307</v>
@@ -24396,10 +24226,10 @@
         <v>30695</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>982</v>
+        <v>962</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>983</v>
+        <v>963</v>
       </c>
       <c r="H53" s="7">
         <v>919154686</v>
@@ -24410,7 +24240,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>976</v>
+        <v>956</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>310</v>
@@ -24422,10 +24252,10 @@
         <v>31036</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>944</v>
+        <v>924</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>984</v>
+        <v>964</v>
       </c>
       <c r="H54" s="7">
         <v>944834000</v>
@@ -24436,7 +24266,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>337</v>
@@ -24448,10 +24278,10 @@
         <v>34221</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>986</v>
+        <v>966</v>
       </c>
       <c r="H55" s="7">
         <v>814177686</v>
@@ -24462,7 +24292,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>340</v>
@@ -24474,10 +24304,10 @@
         <v>29443</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>987</v>
+        <v>967</v>
       </c>
       <c r="H56" s="7">
         <v>915834000</v>
@@ -24488,7 +24318,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>343</v>
@@ -24500,10 +24330,10 @@
         <v>31979</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>988</v>
+        <v>968</v>
       </c>
       <c r="H57" s="7">
         <v>916621787</v>
@@ -24514,7 +24344,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>346</v>
@@ -24526,10 +24356,10 @@
         <v>28542</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>989</v>
+        <v>969</v>
       </c>
       <c r="H58" s="7">
         <v>913504171</v>
@@ -24540,7 +24370,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>349</v>
@@ -24552,10 +24382,10 @@
         <v>30185</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>990</v>
+        <v>970</v>
       </c>
       <c r="H59" s="7">
         <v>915220882</v>
@@ -24566,7 +24396,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>352</v>
@@ -24578,10 +24408,10 @@
         <v>28136</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>991</v>
+        <v>971</v>
       </c>
       <c r="H60" s="7">
         <v>919682692</v>
@@ -24592,7 +24422,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>355</v>
@@ -24604,10 +24434,10 @@
         <v>31701</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>944</v>
+        <v>924</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>992</v>
+        <v>972</v>
       </c>
       <c r="H61" s="7">
         <v>912991988</v>
@@ -24618,7 +24448,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>391</v>
@@ -24630,10 +24460,10 @@
         <v>28754</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>994</v>
+        <v>974</v>
       </c>
       <c r="H62" s="7">
         <v>919663111</v>
@@ -24644,7 +24474,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>394</v>
@@ -24656,10 +24486,10 @@
         <v>27911</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>995</v>
+        <v>975</v>
       </c>
       <c r="H63" s="7">
         <v>917003681</v>
@@ -24670,7 +24500,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>397</v>
@@ -24682,10 +24512,10 @@
         <v>32832</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>996</v>
+        <v>976</v>
       </c>
       <c r="H64" s="7">
         <v>911201189</v>
@@ -24696,7 +24526,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>400</v>
@@ -24708,10 +24538,10 @@
         <v>31936</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>997</v>
+        <v>977</v>
       </c>
       <c r="H65" s="7">
         <v>919080687</v>
@@ -24722,7 +24552,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>403</v>
@@ -24734,10 +24564,10 @@
         <v>31659</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>944</v>
+        <v>924</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>998</v>
+        <v>978</v>
       </c>
       <c r="H66" s="7">
         <v>833365333</v>
@@ -24748,7 +24578,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>999</v>
+        <v>979</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>418</v>
@@ -24760,10 +24590,10 @@
         <v>28907</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="H67" s="7">
         <v>916993000</v>
@@ -24774,7 +24604,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>999</v>
+        <v>979</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>421</v>
@@ -24786,10 +24616,10 @@
         <v>29951</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>1001</v>
+        <v>981</v>
       </c>
       <c r="H68" s="7">
         <v>916638668</v>
@@ -24800,7 +24630,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>999</v>
+        <v>979</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>424</v>
@@ -24812,10 +24642,10 @@
         <v>30136</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>1002</v>
+        <v>982</v>
       </c>
       <c r="H69" s="7">
         <v>912980266</v>
@@ -24826,7 +24656,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>999</v>
+        <v>979</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>427</v>
@@ -24838,10 +24668,10 @@
         <v>31992</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>1003</v>
+        <v>983</v>
       </c>
       <c r="H70" s="7">
         <v>913282195</v>
@@ -24852,7 +24682,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>999</v>
+        <v>979</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>430</v>
@@ -24864,10 +24694,10 @@
         <v>31065</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>1004</v>
+        <v>984</v>
       </c>
       <c r="H71" s="7">
         <v>912964696</v>
@@ -24878,7 +24708,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>999</v>
+        <v>979</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>433</v>
@@ -24890,10 +24720,10 @@
         <v>28836</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>1005</v>
+        <v>985</v>
       </c>
       <c r="H72" s="7">
         <v>916084558</v>
@@ -24904,7 +24734,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>999</v>
+        <v>979</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>436</v>
@@ -24916,10 +24746,10 @@
         <v>29883</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>1006</v>
+        <v>986</v>
       </c>
       <c r="H73" s="7">
         <v>914012626</v>
@@ -24930,7 +24760,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>999</v>
+        <v>979</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>439</v>
@@ -24942,10 +24772,10 @@
         <v>28977</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>1007</v>
+        <v>987</v>
       </c>
       <c r="H74" s="7">
         <v>942904222</v>
@@ -24956,7 +24786,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>999</v>
+        <v>979</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>442</v>
@@ -24968,10 +24798,10 @@
         <v>31081</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>1008</v>
+        <v>988</v>
       </c>
       <c r="H75" s="7">
         <v>916313368</v>
@@ -24982,7 +24812,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>999</v>
+        <v>979</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>445</v>
@@ -24994,10 +24824,10 @@
         <v>28783</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>1009</v>
+        <v>989</v>
       </c>
       <c r="H76" s="7">
         <v>947545777</v>
@@ -25008,7 +24838,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>999</v>
+        <v>979</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>448</v>
@@ -25020,10 +24850,10 @@
         <v>28793</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>1010</v>
+        <v>990</v>
       </c>
       <c r="H77" s="7">
         <v>912776868</v>
@@ -25034,7 +24864,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>999</v>
+        <v>979</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>451</v>
@@ -25046,10 +24876,10 @@
         <v>31515</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>926</v>
+        <v>906</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>1011</v>
+        <v>991</v>
       </c>
       <c r="H78" s="7">
         <v>945130486</v>
@@ -25060,7 +24890,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>999</v>
+        <v>979</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>454</v>
@@ -25072,10 +24902,10 @@
         <v>29146</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>944</v>
+        <v>924</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>1012</v>
+        <v>992</v>
       </c>
       <c r="H79" s="7">
         <v>913389699</v>
@@ -25086,7 +24916,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>484</v>
@@ -25098,10 +24928,10 @@
         <v>31166</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>1014</v>
+        <v>994</v>
       </c>
       <c r="H80" s="7">
         <v>918013222</v>
@@ -25112,7 +24942,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>487</v>
@@ -25124,10 +24954,10 @@
         <v>26535</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>1015</v>
+        <v>995</v>
       </c>
       <c r="H81" s="7">
         <v>912201468</v>
@@ -25138,7 +24968,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>490</v>
@@ -25150,10 +24980,10 @@
         <v>29957</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>1016</v>
+        <v>996</v>
       </c>
       <c r="H82" s="7">
         <v>825161357</v>
@@ -25164,7 +24994,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>493</v>
@@ -25176,10 +25006,10 @@
         <v>26461</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>1017</v>
+        <v>997</v>
       </c>
       <c r="H83" s="7">
         <v>913244267</v>
@@ -25190,7 +25020,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>496</v>
@@ -25202,10 +25032,10 @@
         <v>28884</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>926</v>
+        <v>906</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>1018</v>
+        <v>998</v>
       </c>
       <c r="H84" s="7">
         <v>946716699</v>
@@ -25216,7 +25046,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>499</v>
@@ -25228,10 +25058,10 @@
         <v>30935</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>1019</v>
+        <v>999</v>
       </c>
       <c r="H85" s="7">
         <v>943074777</v>
@@ -25242,7 +25072,7 @@
         <v>84</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>502</v>
@@ -25254,10 +25084,10 @@
         <v>32187</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>926</v>
+        <v>906</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>1020</v>
+        <v>1000</v>
       </c>
       <c r="H86" s="7">
         <v>943307007</v>
@@ -25268,7 +25098,7 @@
         <v>85</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>505</v>
@@ -25280,10 +25110,10 @@
         <v>32448</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>1021</v>
+        <v>1001</v>
       </c>
       <c r="H87" s="7">
         <v>913339683</v>
@@ -25294,7 +25124,7 @@
         <v>86</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>508</v>
@@ -25306,10 +25136,10 @@
         <v>30198</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>944</v>
+        <v>924</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>1022</v>
+        <v>1002</v>
       </c>
       <c r="H88" s="7">
         <v>945116677</v>
@@ -25320,7 +25150,7 @@
         <v>87</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>1023</v>
+        <v>1003</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>578</v>
@@ -25332,10 +25162,10 @@
         <v>30738</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>1024</v>
+        <v>1004</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>1025</v>
+        <v>1005</v>
       </c>
       <c r="H89" s="7">
         <v>916851355</v>
@@ -25346,7 +25176,7 @@
         <v>88</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>1023</v>
+        <v>1003</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>580</v>
@@ -25358,10 +25188,10 @@
         <v>31759</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>1024</v>
+        <v>1004</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>1026</v>
+        <v>1006</v>
       </c>
       <c r="H90" s="7">
         <v>915555452</v>
@@ -25372,7 +25202,7 @@
         <v>89</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>1023</v>
+        <v>1003</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>582</v>
@@ -25384,10 +25214,10 @@
         <v>29859</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>1024</v>
+        <v>1004</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>1027</v>
+        <v>1007</v>
       </c>
       <c r="H91" s="7">
         <v>915773775</v>
@@ -25398,7 +25228,7 @@
         <v>90</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>1023</v>
+        <v>1003</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>585</v>
@@ -25410,10 +25240,10 @@
         <v>29102</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>1028</v>
+        <v>1008</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>1029</v>
+        <v>1009</v>
       </c>
       <c r="H92" s="7">
         <v>913296045</v>
@@ -25424,7 +25254,7 @@
         <v>91</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>514</v>
@@ -25436,10 +25266,10 @@
         <v>30317</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>1024</v>
+        <v>1004</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>1031</v>
+        <v>1011</v>
       </c>
       <c r="H93" s="7">
         <v>913849865</v>
@@ -25450,7 +25280,7 @@
         <v>92</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>517</v>
@@ -25462,10 +25292,10 @@
         <v>30963</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>1024</v>
+        <v>1004</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>1032</v>
+        <v>1012</v>
       </c>
       <c r="H94" s="7">
         <v>888222886</v>
@@ -25476,7 +25306,7 @@
         <v>93</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>519</v>
@@ -25488,10 +25318,10 @@
         <v>35675</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>1024</v>
+        <v>1004</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>1033</v>
+        <v>1013</v>
       </c>
       <c r="H95" s="7">
         <v>943591997</v>
@@ -25502,7 +25332,7 @@
         <v>94</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>522</v>
@@ -25514,10 +25344,10 @@
         <v>32362</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>1024</v>
+        <v>1004</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>1034</v>
+        <v>1014</v>
       </c>
       <c r="H96" s="7">
         <v>949844489</v>
@@ -25528,7 +25358,7 @@
         <v>95</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>525</v>
@@ -25540,10 +25370,10 @@
         <v>34155</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>1028</v>
+        <v>1008</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>1035</v>
+        <v>1015</v>
       </c>
       <c r="H97" s="7">
         <v>941068993</v>
@@ -25554,7 +25384,7 @@
         <v>96</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>1036</v>
+        <v>1016</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>572</v>
@@ -25566,10 +25396,10 @@
         <v>33010</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>1024</v>
+        <v>1004</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>1037</v>
+        <v>1017</v>
       </c>
       <c r="H98" s="7">
         <v>911486686</v>
@@ -25580,7 +25410,7 @@
         <v>97</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>1036</v>
+        <v>1016</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>575</v>
@@ -25592,10 +25422,10 @@
         <v>32772</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>1028</v>
+        <v>1008</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>1038</v>
+        <v>1018</v>
       </c>
       <c r="H99" s="7">
         <v>913183089</v>
@@ -25606,7 +25436,7 @@
         <v>98</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>1039</v>
+        <v>1019</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>528</v>
@@ -25618,10 +25448,10 @@
         <v>30061</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>1041</v>
+        <v>1021</v>
       </c>
       <c r="H100" s="7">
         <v>942466222</v>
@@ -25632,7 +25462,7 @@
         <v>99</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>1039</v>
+        <v>1019</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>531</v>
@@ -25644,10 +25474,10 @@
         <v>35146</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>1042</v>
+        <v>1022</v>
       </c>
       <c r="H101" s="7">
         <v>888360396</v>
@@ -25658,7 +25488,7 @@
         <v>100</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>1039</v>
+        <v>1019</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>534</v>
@@ -25670,10 +25500,10 @@
         <v>32643</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>1043</v>
+        <v>1023</v>
       </c>
       <c r="H102" s="7">
         <v>911244989</v>
@@ -25684,7 +25514,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>1039</v>
+        <v>1019</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>39</v>
@@ -25696,10 +25526,10 @@
         <v>29910</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>1044</v>
+        <v>1024</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>1045</v>
+        <v>1025</v>
       </c>
       <c r="H103" s="7">
         <v>912634868</v>
@@ -25710,7 +25540,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>1039</v>
+        <v>1019</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>540</v>
@@ -25722,10 +25552,10 @@
         <v>30578</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>1046</v>
+        <v>1026</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>1047</v>
+        <v>1027</v>
       </c>
       <c r="H104" s="7">
         <v>942271189</v>
@@ -25736,7 +25566,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>1039</v>
+        <v>1019</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>537</v>
@@ -25748,10 +25578,10 @@
         <v>32061</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>1046</v>
+        <v>1026</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>1048</v>
+        <v>1028</v>
       </c>
       <c r="H105" s="7">
         <v>948433188</v>
@@ -25762,7 +25592,7 @@
         <v>104</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>1039</v>
+        <v>1019</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>543</v>
@@ -25774,10 +25604,10 @@
         <v>29801</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>1046</v>
+        <v>1026</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>1049</v>
+        <v>1029</v>
       </c>
       <c r="H106" s="7">
         <v>912777078</v>
@@ -25788,7 +25618,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>1039</v>
+        <v>1019</v>
       </c>
       <c r="C107" s="5" t="s">
         <v>546</v>
@@ -25800,10 +25630,10 @@
         <v>27484</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>1046</v>
+        <v>1026</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="H107" s="7">
         <v>912577679</v>
@@ -25814,7 +25644,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>1039</v>
+        <v>1019</v>
       </c>
       <c r="C108" s="5" t="s">
         <v>549</v>
@@ -25826,10 +25656,10 @@
         <v>34742</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>1046</v>
+        <v>1026</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>1051</v>
+        <v>1031</v>
       </c>
       <c r="H108" s="7">
         <v>913122995</v>
@@ -25840,7 +25670,7 @@
         <v>107</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>1039</v>
+        <v>1019</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>54</v>
@@ -25852,10 +25682,10 @@
         <v>29922</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>1046</v>
+        <v>1026</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>1052</v>
+        <v>1032</v>
       </c>
       <c r="H109" s="7">
         <v>914565181</v>
@@ -25866,7 +25696,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>1039</v>
+        <v>1019</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>552</v>
@@ -25878,10 +25708,10 @@
         <v>29924</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>1046</v>
+        <v>1026</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>1053</v>
+        <v>1033</v>
       </c>
       <c r="H110" s="7">
         <v>914626626</v>
@@ -25892,7 +25722,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>1039</v>
+        <v>1019</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>554</v>
@@ -25904,10 +25734,10 @@
         <v>27839</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>1046</v>
+        <v>1026</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>1054</v>
+        <v>1034</v>
       </c>
       <c r="H111" s="7">
         <v>916840999</v>
@@ -25918,7 +25748,7 @@
         <v>110</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>1039</v>
+        <v>1019</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>557</v>
@@ -25930,10 +25760,10 @@
         <v>34213</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>1046</v>
+        <v>1026</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>1055</v>
+        <v>1035</v>
       </c>
       <c r="H112" s="7">
         <v>912960386</v>
@@ -25944,7 +25774,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>1039</v>
+        <v>1019</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>560</v>
@@ -25956,10 +25786,10 @@
         <v>31071</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>1046</v>
+        <v>1026</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>1056</v>
+        <v>1036</v>
       </c>
       <c r="H113" s="7">
         <v>916360325</v>
@@ -25970,7 +25800,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>1039</v>
+        <v>1019</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>563</v>
@@ -25982,10 +25812,10 @@
         <v>30850</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>1046</v>
+        <v>1026</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>1057</v>
+        <v>1037</v>
       </c>
       <c r="H114" s="7">
         <v>942795027</v>
@@ -25996,7 +25826,7 @@
         <v>113</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>1039</v>
+        <v>1019</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>566</v>
@@ -26008,10 +25838,10 @@
         <v>29015</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>1046</v>
+        <v>1026</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>1058</v>
+        <v>1038</v>
       </c>
       <c r="H115" s="7">
         <v>912581259</v>
@@ -26022,7 +25852,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>41</v>
@@ -26034,10 +25864,10 @@
         <v>29717</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>1060</v>
+        <v>1040</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>1061</v>
+        <v>1041</v>
       </c>
       <c r="H116" s="7">
         <v>911601999</v>
@@ -26048,7 +25878,7 @@
         <v>115</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>46</v>
@@ -26060,10 +25890,10 @@
         <v>30609</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>1062</v>
+        <v>1042</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>1063</v>
+        <v>1043</v>
       </c>
       <c r="H117" s="7">
         <v>918474583</v>
@@ -26074,7 +25904,7 @@
         <v>116</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>48</v>
@@ -26086,10 +25916,10 @@
         <v>29594</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>1062</v>
+        <v>1042</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>1064</v>
+        <v>1044</v>
       </c>
       <c r="H118" s="7">
         <v>913282523</v>
@@ -26100,7 +25930,7 @@
         <v>117</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C119" s="5" t="s">
         <v>50</v>
@@ -26112,10 +25942,10 @@
         <v>25447</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>1065</v>
+        <v>1045</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>1066</v>
+        <v>1046</v>
       </c>
       <c r="H119" s="7">
         <v>913282010</v>
@@ -26126,7 +25956,7 @@
         <v>118</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C120" s="5" t="s">
         <v>52</v>
@@ -26138,10 +25968,10 @@
         <v>29882</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>1067</v>
+        <v>1047</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>1068</v>
+        <v>1048</v>
       </c>
       <c r="H120" s="7">
         <v>915171567</v>
@@ -26152,22 +25982,22 @@
         <v>119</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>1069</v>
+        <v>1049</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>1070</v>
+        <v>1050</v>
       </c>
       <c r="E121" s="6">
         <v>25150</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>1071</v>
+        <v>1051</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>1072</v>
+        <v>1052</v>
       </c>
       <c r="H121" s="7">
         <v>913869189</v>
@@ -26178,22 +26008,22 @@
         <v>120</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>1073</v>
+        <v>1053</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>1074</v>
+        <v>1054</v>
       </c>
       <c r="E122" s="9">
         <v>26605</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>1071</v>
+        <v>1051</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>1075</v>
+        <v>1055</v>
       </c>
       <c r="H122" s="7">
         <v>916466451</v>
@@ -26204,22 +26034,22 @@
         <v>121</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>1076</v>
+        <v>1056</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>1077</v>
+        <v>1057</v>
       </c>
       <c r="E123" s="6">
         <v>27437</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>1071</v>
+        <v>1051</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>1078</v>
+        <v>1058</v>
       </c>
       <c r="H123" s="7">
         <v>913592422</v>
@@ -26230,7 +26060,7 @@
         <v>122</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C124" s="5" t="s">
         <v>56</v>
@@ -26242,10 +26072,10 @@
         <v>30435</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>1067</v>
+        <v>1047</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>1079</v>
+        <v>1059</v>
       </c>
       <c r="H124" s="7">
         <v>918666808</v>
@@ -26256,7 +26086,7 @@
         <v>123</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>58</v>
@@ -26268,10 +26098,10 @@
         <v>28789</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>1062</v>
+        <v>1042</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>1080</v>
+        <v>1060</v>
       </c>
       <c r="H125" s="7">
         <v>918581978</v>
@@ -26282,7 +26112,7 @@
         <v>124</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>60</v>
@@ -26294,10 +26124,10 @@
         <v>28537</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>1081</v>
+        <v>1061</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>1082</v>
+        <v>1062</v>
       </c>
       <c r="H126" s="7">
         <v>943128668</v>
@@ -26308,7 +26138,7 @@
         <v>125</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>62</v>
@@ -26320,10 +26150,10 @@
         <v>29255</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>1083</v>
+        <v>1063</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>1084</v>
+        <v>1064</v>
       </c>
       <c r="H127" s="7">
         <v>945116689</v>
@@ -26334,7 +26164,7 @@
         <v>126</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C128" s="8" t="s">
         <v>64</v>
@@ -26346,10 +26176,10 @@
         <v>31938</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>1067</v>
+        <v>1047</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>1085</v>
+        <v>1065</v>
       </c>
       <c r="H128" s="7">
         <v>912191516</v>
@@ -26360,7 +26190,7 @@
         <v>127</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C129" s="5" t="s">
         <v>66</v>
@@ -26372,10 +26202,10 @@
         <v>29414</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>1083</v>
+        <v>1063</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>1086</v>
+        <v>1066</v>
       </c>
       <c r="H129" s="7">
         <v>947118999</v>
@@ -26386,7 +26216,7 @@
         <v>128</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C130" s="5" t="s">
         <v>68</v>
@@ -26398,10 +26228,10 @@
         <v>28823</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>1062</v>
+        <v>1042</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>1087</v>
+        <v>1067</v>
       </c>
       <c r="H130" s="7">
         <v>912211382</v>
@@ -26412,7 +26242,7 @@
         <v>129</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>70</v>
@@ -26424,10 +26254,10 @@
         <v>32201</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>1081</v>
+        <v>1061</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>1088</v>
+        <v>1068</v>
       </c>
       <c r="H131" s="7">
         <v>948517222</v>
@@ -26438,7 +26268,7 @@
         <v>130</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>72</v>
@@ -26450,10 +26280,10 @@
         <v>27746</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>1062</v>
+        <v>1042</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>1089</v>
+        <v>1069</v>
       </c>
       <c r="H132" s="7">
         <v>912362552</v>
@@ -26464,7 +26294,7 @@
         <v>131</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>74</v>
@@ -26476,10 +26306,10 @@
         <v>28493</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>1067</v>
+        <v>1047</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>1090</v>
+        <v>1070</v>
       </c>
       <c r="H133" s="7">
         <v>914838555</v>
@@ -26490,7 +26320,7 @@
         <v>132</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>76</v>
@@ -26502,10 +26332,10 @@
         <v>27776</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>1083</v>
+        <v>1063</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>1091</v>
+        <v>1071</v>
       </c>
       <c r="H134" s="7">
         <v>915687676</v>
@@ -26516,22 +26346,22 @@
         <v>133</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>1092</v>
+        <v>1072</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>1093</v>
+        <v>1073</v>
       </c>
       <c r="E135" s="6">
         <v>26794</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>1071</v>
+        <v>1051</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>1094</v>
+        <v>1074</v>
       </c>
       <c r="H135" s="7">
         <v>911121973</v>
@@ -26542,22 +26372,22 @@
         <v>134</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>1095</v>
+        <v>1075</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>1096</v>
+        <v>1076</v>
       </c>
       <c r="E136" s="6">
         <v>28415</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>1071</v>
+        <v>1051</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>1097</v>
+        <v>1077</v>
       </c>
       <c r="H136" s="7">
         <v>915893067</v>
@@ -26568,22 +26398,22 @@
         <v>135</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>1098</v>
+        <v>1078</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>1099</v>
+        <v>1079</v>
       </c>
       <c r="E137" s="6">
         <v>26672</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>1071</v>
+        <v>1051</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>1100</v>
+        <v>1080</v>
       </c>
       <c r="H137" s="7">
         <v>918004889</v>
@@ -26594,7 +26424,7 @@
         <v>136</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="C138" s="5" t="s">
         <v>78</v>
@@ -26606,10 +26436,10 @@
         <v>33158</v>
       </c>
       <c r="F138" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>1101</v>
+        <v>1081</v>
       </c>
       <c r="H138" s="7">
         <v>948529669</v>
@@ -26620,7 +26450,7 @@
         <v>137</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>80</v>
@@ -26632,10 +26462,10 @@
         <v>30256</v>
       </c>
       <c r="F139" s="11" t="s">
-        <v>926</v>
+        <v>906</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>1102</v>
+        <v>1082</v>
       </c>
       <c r="H139" s="12">
         <v>945688198</v>
@@ -26646,7 +26476,7 @@
         <v>138</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>946</v>
+        <v>926</v>
       </c>
       <c r="C140" s="5" t="s">
         <v>129</v>
@@ -26658,10 +26488,10 @@
         <v>31887</v>
       </c>
       <c r="F140" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>1103</v>
+        <v>1083</v>
       </c>
       <c r="H140" s="7">
         <v>941123233</v>
@@ -26672,7 +26502,7 @@
         <v>139</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>946</v>
+        <v>926</v>
       </c>
       <c r="C141" s="5" t="s">
         <v>132</v>
@@ -26684,10 +26514,10 @@
         <v>34495</v>
       </c>
       <c r="F141" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>1104</v>
+        <v>1084</v>
       </c>
       <c r="H141" s="7">
         <v>856020555</v>
@@ -26698,7 +26528,7 @@
         <v>140</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>946</v>
+        <v>926</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>135</v>
@@ -26710,10 +26540,10 @@
         <v>32475</v>
       </c>
       <c r="F142" s="11" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G142" s="8" t="s">
-        <v>1105</v>
+        <v>1085</v>
       </c>
       <c r="H142" s="12">
         <v>819889698</v>
@@ -26724,7 +26554,7 @@
         <v>141</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>946</v>
+        <v>926</v>
       </c>
       <c r="C143" s="5" t="s">
         <v>138</v>
@@ -26736,10 +26566,10 @@
         <v>32770</v>
       </c>
       <c r="F143" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>1106</v>
+        <v>1086</v>
       </c>
       <c r="H143" s="7">
         <v>918793045</v>
@@ -26750,7 +26580,7 @@
         <v>142</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>951</v>
+        <v>931</v>
       </c>
       <c r="C144" s="5" t="s">
         <v>157</v>
@@ -26762,10 +26592,10 @@
         <v>30530</v>
       </c>
       <c r="F144" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>1107</v>
+        <v>1087</v>
       </c>
       <c r="H144" s="7">
         <v>916833223</v>
@@ -26776,7 +26606,7 @@
         <v>143</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>951</v>
+        <v>931</v>
       </c>
       <c r="C145" s="5" t="s">
         <v>160</v>
@@ -26788,10 +26618,10 @@
         <v>31966</v>
       </c>
       <c r="F145" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>1108</v>
+        <v>1088</v>
       </c>
       <c r="H145" s="7">
         <v>912104433</v>
@@ -26802,7 +26632,7 @@
         <v>144</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>951</v>
+        <v>931</v>
       </c>
       <c r="C146" s="5" t="s">
         <v>154</v>
@@ -26814,10 +26644,10 @@
         <v>33221</v>
       </c>
       <c r="F146" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>1109</v>
+        <v>1089</v>
       </c>
       <c r="H146" s="7">
         <v>911312990</v>
@@ -26828,7 +26658,7 @@
         <v>145</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>951</v>
+        <v>931</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>163</v>
@@ -26840,10 +26670,10 @@
         <v>33134</v>
       </c>
       <c r="F147" s="11" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G147" s="8" t="s">
-        <v>1110</v>
+        <v>1090</v>
       </c>
       <c r="H147" s="12">
         <v>911747266</v>
@@ -26854,7 +26684,7 @@
         <v>146</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="C148" s="5" t="s">
         <v>187</v>
@@ -26866,10 +26696,10 @@
         <v>30622</v>
       </c>
       <c r="F148" s="10" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>1111</v>
+        <v>1091</v>
       </c>
       <c r="H148" s="7">
         <v>849023555</v>
@@ -26880,7 +26710,7 @@
         <v>147</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="C149" s="5" t="s">
         <v>190</v>
@@ -26892,10 +26722,10 @@
         <v>30550</v>
       </c>
       <c r="F149" s="10" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>1112</v>
+        <v>1092</v>
       </c>
       <c r="H149" s="7">
         <v>816162222</v>
@@ -26906,7 +26736,7 @@
         <v>148</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="C150" s="8" t="s">
         <v>193</v>
@@ -26918,10 +26748,10 @@
         <v>29672</v>
       </c>
       <c r="F150" s="11" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G150" s="8" t="s">
-        <v>1113</v>
+        <v>1093</v>
       </c>
       <c r="H150" s="12">
         <v>886761981</v>
@@ -26932,7 +26762,7 @@
         <v>149</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="C151" s="5" t="s">
         <v>196</v>
@@ -26944,10 +26774,10 @@
         <v>30934</v>
       </c>
       <c r="F151" s="10" t="s">
-        <v>926</v>
+        <v>906</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>1114</v>
+        <v>1094</v>
       </c>
       <c r="H151" s="7">
         <v>914899546</v>
@@ -26958,7 +26788,7 @@
         <v>150</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="C152" s="5" t="s">
         <v>199</v>
@@ -26970,10 +26800,10 @@
         <v>33239</v>
       </c>
       <c r="F152" s="10" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>1115</v>
+        <v>1095</v>
       </c>
       <c r="H152" s="7">
         <v>886581281</v>
@@ -26984,7 +26814,7 @@
         <v>151</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="C153" s="8" t="s">
         <v>226</v>
@@ -26996,10 +26826,10 @@
         <v>31722</v>
       </c>
       <c r="F153" s="11" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G153" s="8" t="s">
-        <v>1116</v>
+        <v>1096</v>
       </c>
       <c r="H153" s="12">
         <v>835155999</v>
@@ -27010,7 +26840,7 @@
         <v>152</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="C154" s="5" t="s">
         <v>229</v>
@@ -27022,10 +26852,10 @@
         <v>32239</v>
       </c>
       <c r="F154" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>1117</v>
+        <v>1097</v>
       </c>
       <c r="H154" s="7">
         <v>917677600</v>
@@ -27036,7 +26866,7 @@
         <v>153</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="C155" s="5" t="s">
         <v>232</v>
@@ -27048,10 +26878,10 @@
         <v>24907</v>
       </c>
       <c r="F155" s="10" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>1118</v>
+        <v>1098</v>
       </c>
       <c r="H155" s="7">
         <v>949239366</v>
@@ -27062,7 +26892,7 @@
         <v>154</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="C156" s="5" t="s">
         <v>235</v>
@@ -27074,10 +26904,10 @@
         <v>26444</v>
       </c>
       <c r="F156" s="10" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>1119</v>
+        <v>1099</v>
       </c>
       <c r="H156" s="7">
         <v>916279727</v>
@@ -27088,7 +26918,7 @@
         <v>155</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="C157" s="5" t="s">
         <v>238</v>
@@ -27100,10 +26930,10 @@
         <v>29492</v>
       </c>
       <c r="F157" s="10" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>1120</v>
+        <v>1100</v>
       </c>
       <c r="H157" s="7">
         <v>914913145</v>
@@ -27114,7 +26944,7 @@
         <v>156</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="C158" s="5" t="s">
         <v>241</v>
@@ -27126,10 +26956,10 @@
         <v>32754</v>
       </c>
       <c r="F158" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>1121</v>
+        <v>1101</v>
       </c>
       <c r="H158" s="7">
         <v>833676186</v>
@@ -27140,7 +26970,7 @@
         <v>157</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="C159" s="8" t="s">
         <v>244</v>
@@ -27152,10 +26982,10 @@
         <v>34163</v>
       </c>
       <c r="F159" s="11" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>1122</v>
+        <v>1102</v>
       </c>
       <c r="H159" s="12">
         <v>833313793</v>
@@ -27166,7 +26996,7 @@
         <v>158</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="C160" s="5" t="s">
         <v>247</v>
@@ -27178,10 +27008,10 @@
         <v>32583</v>
       </c>
       <c r="F160" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>1123</v>
+        <v>1103</v>
       </c>
       <c r="H160" s="7">
         <v>941631989</v>
@@ -27192,7 +27022,7 @@
         <v>159</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="C161" s="5" t="s">
         <v>250</v>
@@ -27204,10 +27034,10 @@
         <v>34157</v>
       </c>
       <c r="F161" s="10" t="s">
-        <v>926</v>
+        <v>906</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>1124</v>
+        <v>1104</v>
       </c>
       <c r="H161" s="7">
         <v>348537004</v>
@@ -27218,7 +27048,7 @@
         <v>160</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="C162" s="5" t="s">
         <v>253</v>
@@ -27230,10 +27060,10 @@
         <v>34695</v>
       </c>
       <c r="F162" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>1125</v>
+        <v>1105</v>
       </c>
       <c r="H162" s="7">
         <v>858332211</v>
@@ -27244,7 +27074,7 @@
         <v>161</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="C163" s="5" t="s">
         <v>256</v>
@@ -27256,10 +27086,10 @@
         <v>33530</v>
       </c>
       <c r="F163" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>1126</v>
+        <v>1106</v>
       </c>
       <c r="H163" s="7">
         <v>846334686</v>
@@ -27270,7 +27100,7 @@
         <v>162</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="C164" s="5" t="s">
         <v>259</v>
@@ -27282,10 +27112,10 @@
         <v>32312</v>
       </c>
       <c r="F164" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>1127</v>
+        <v>1107</v>
       </c>
       <c r="H164" s="7">
         <v>912490102</v>
@@ -27296,7 +27126,7 @@
         <v>163</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>976</v>
+        <v>956</v>
       </c>
       <c r="C165" s="5" t="s">
         <v>280</v>
@@ -27308,10 +27138,10 @@
         <v>32599</v>
       </c>
       <c r="F165" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>1128</v>
+        <v>1108</v>
       </c>
       <c r="H165" s="7">
         <v>914962262</v>
@@ -27322,7 +27152,7 @@
         <v>164</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>976</v>
+        <v>956</v>
       </c>
       <c r="C166" s="5" t="s">
         <v>283</v>
@@ -27334,10 +27164,10 @@
         <v>29330</v>
       </c>
       <c r="F166" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>1129</v>
+        <v>1109</v>
       </c>
       <c r="H166" s="7">
         <v>947450444</v>
@@ -27348,7 +27178,7 @@
         <v>165</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>976</v>
+        <v>956</v>
       </c>
       <c r="C167" s="5" t="s">
         <v>286</v>
@@ -27360,10 +27190,10 @@
         <v>33746</v>
       </c>
       <c r="F167" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>1130</v>
+        <v>1110</v>
       </c>
       <c r="H167" s="7">
         <v>917022592</v>
@@ -27374,7 +27204,7 @@
         <v>166</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>976</v>
+        <v>956</v>
       </c>
       <c r="C168" s="5" t="s">
         <v>289</v>
@@ -27386,10 +27216,10 @@
         <v>32865</v>
       </c>
       <c r="F168" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>1131</v>
+        <v>1111</v>
       </c>
       <c r="H168" s="7">
         <v>829861128</v>
@@ -27400,7 +27230,7 @@
         <v>167</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
       <c r="C169" s="5" t="s">
         <v>313</v>
@@ -27412,10 +27242,10 @@
         <v>35282</v>
       </c>
       <c r="F169" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>1132</v>
+        <v>1112</v>
       </c>
       <c r="H169" s="7">
         <v>941092376</v>
@@ -27426,7 +27256,7 @@
         <v>168</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
       <c r="C170" s="5" t="s">
         <v>316</v>
@@ -27438,10 +27268,10 @@
         <v>36880</v>
       </c>
       <c r="F170" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>1133</v>
+        <v>1113</v>
       </c>
       <c r="H170" s="7">
         <v>917600366</v>
@@ -27452,7 +27282,7 @@
         <v>169</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
       <c r="C171" s="5" t="s">
         <v>319</v>
@@ -27464,10 +27294,10 @@
         <v>31516</v>
       </c>
       <c r="F171" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>1134</v>
+        <v>1114</v>
       </c>
       <c r="H171" s="7">
         <v>949328222</v>
@@ -27478,7 +27308,7 @@
         <v>170</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
       <c r="C172" s="8" t="s">
         <v>322</v>
@@ -27490,10 +27320,10 @@
         <v>34278</v>
       </c>
       <c r="F172" s="11" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G172" s="8" t="s">
-        <v>1135</v>
+        <v>1115</v>
       </c>
       <c r="H172" s="12">
         <v>835850333</v>
@@ -27504,7 +27334,7 @@
         <v>171</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
       <c r="C173" s="5" t="s">
         <v>325</v>
@@ -27516,10 +27346,10 @@
         <v>30623</v>
       </c>
       <c r="F173" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>1136</v>
+        <v>1116</v>
       </c>
       <c r="H173" s="7">
         <v>966826781</v>
@@ -27530,7 +27360,7 @@
         <v>172</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
       <c r="C174" s="5" t="s">
         <v>328</v>
@@ -27542,10 +27372,10 @@
         <v>33133</v>
       </c>
       <c r="F174" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>1137</v>
+        <v>1117</v>
       </c>
       <c r="H174" s="7">
         <v>948617990</v>
@@ -27556,7 +27386,7 @@
         <v>173</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
       <c r="C175" s="5" t="s">
         <v>331</v>
@@ -27568,10 +27398,10 @@
         <v>31134</v>
       </c>
       <c r="F175" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>1138</v>
+        <v>1118</v>
       </c>
       <c r="H175" s="7">
         <v>816212185</v>
@@ -27582,7 +27412,7 @@
         <v>174</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
       <c r="C176" s="5" t="s">
         <v>334</v>
@@ -27594,10 +27424,10 @@
         <v>32603</v>
       </c>
       <c r="F176" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>1139</v>
+        <v>1119</v>
       </c>
       <c r="H176" s="7">
         <v>947436389</v>
@@ -27608,7 +27438,7 @@
         <v>175</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="C177" s="8" t="s">
         <v>361</v>
@@ -27620,10 +27450,10 @@
         <v>34706</v>
       </c>
       <c r="F177" s="11" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G177" s="8" t="s">
-        <v>1140</v>
+        <v>1120</v>
       </c>
       <c r="H177" s="12">
         <v>914333829</v>
@@ -27634,7 +27464,7 @@
         <v>176</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="C178" s="5" t="s">
         <v>364</v>
@@ -27646,10 +27476,10 @@
         <v>38395</v>
       </c>
       <c r="F178" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G178" s="5" t="s">
-        <v>1141</v>
+        <v>1121</v>
       </c>
       <c r="H178" s="7">
         <v>916456005</v>
@@ -27660,7 +27490,7 @@
         <v>177</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="C179" s="5" t="s">
         <v>367</v>
@@ -27672,10 +27502,10 @@
         <v>36996</v>
       </c>
       <c r="F179" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>1142</v>
+        <v>1122</v>
       </c>
       <c r="H179" s="7">
         <v>889115401</v>
@@ -27686,7 +27516,7 @@
         <v>178</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="C180" s="5" t="s">
         <v>369</v>
@@ -27698,10 +27528,10 @@
         <v>31558</v>
       </c>
       <c r="F180" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G180" s="5" t="s">
-        <v>1143</v>
+        <v>1123</v>
       </c>
       <c r="H180" s="7">
         <v>818135205</v>
@@ -27712,7 +27542,7 @@
         <v>179</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="C181" s="5" t="s">
         <v>372</v>
@@ -27724,10 +27554,10 @@
         <v>34443</v>
       </c>
       <c r="F181" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>1144</v>
+        <v>1124</v>
       </c>
       <c r="H181" s="7">
         <v>836080419</v>
@@ -27738,7 +27568,7 @@
         <v>180</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="C182" s="5" t="s">
         <v>376</v>
@@ -27750,10 +27580,10 @@
         <v>34359</v>
       </c>
       <c r="F182" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G182" s="5" t="s">
-        <v>1145</v>
+        <v>1125</v>
       </c>
       <c r="H182" s="7">
         <v>835291994</v>
@@ -27764,7 +27594,7 @@
         <v>181</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="C183" s="5" t="s">
         <v>379</v>
@@ -27776,10 +27606,10 @@
         <v>31677</v>
       </c>
       <c r="F183" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G183" s="5" t="s">
-        <v>1146</v>
+        <v>1126</v>
       </c>
       <c r="H183" s="7">
         <v>825349395</v>
@@ -27790,7 +27620,7 @@
         <v>182</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="C184" s="5" t="s">
         <v>382</v>
@@ -27802,10 +27632,10 @@
         <v>36500</v>
       </c>
       <c r="F184" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G184" s="5" t="s">
-        <v>1147</v>
+        <v>1127</v>
       </c>
       <c r="H184" s="7">
         <v>834808871</v>
@@ -27816,7 +27646,7 @@
         <v>183</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="C185" s="5" t="s">
         <v>385</v>
@@ -27828,10 +27658,10 @@
         <v>31093</v>
       </c>
       <c r="F185" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G185" s="5" t="s">
-        <v>1148</v>
+        <v>1128</v>
       </c>
       <c r="H185" s="7">
         <v>912099420</v>
@@ -27842,7 +27672,7 @@
         <v>184</v>
       </c>
       <c r="B186" s="8" t="s">
-        <v>999</v>
+        <v>979</v>
       </c>
       <c r="C186" s="8" t="s">
         <v>406</v>
@@ -27854,10 +27684,10 @@
         <v>33383</v>
       </c>
       <c r="F186" s="11" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G186" s="8" t="s">
-        <v>1149</v>
+        <v>1129</v>
       </c>
       <c r="H186" s="12">
         <v>917936286</v>
@@ -27868,7 +27698,7 @@
         <v>185</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>999</v>
+        <v>979</v>
       </c>
       <c r="C187" s="5" t="s">
         <v>409</v>
@@ -27880,10 +27710,10 @@
         <v>32716</v>
       </c>
       <c r="F187" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G187" s="5" t="s">
-        <v>1150</v>
+        <v>1130</v>
       </c>
       <c r="H187" s="7">
         <v>886133663</v>
@@ -27894,7 +27724,7 @@
         <v>186</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>999</v>
+        <v>979</v>
       </c>
       <c r="C188" s="5" t="s">
         <v>412</v>
@@ -27906,10 +27736,10 @@
         <v>30110</v>
       </c>
       <c r="F188" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G188" s="5" t="s">
-        <v>1151</v>
+        <v>1131</v>
       </c>
       <c r="H188" s="7">
         <v>843068076</v>
@@ -27920,7 +27750,7 @@
         <v>187</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>999</v>
+        <v>979</v>
       </c>
       <c r="C189" s="5" t="s">
         <v>415</v>
@@ -27932,10 +27762,10 @@
         <v>32570</v>
       </c>
       <c r="F189" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>1152</v>
+        <v>1132</v>
       </c>
       <c r="H189" s="7">
         <v>916436123</v>
@@ -27946,7 +27776,7 @@
         <v>188</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="C190" s="5" t="s">
         <v>457</v>
@@ -27958,10 +27788,10 @@
         <v>29777</v>
       </c>
       <c r="F190" s="10" t="s">
-        <v>926</v>
+        <v>906</v>
       </c>
       <c r="G190" s="5" t="s">
-        <v>1153</v>
+        <v>1133</v>
       </c>
       <c r="H190" s="7">
         <v>941747630</v>
@@ -27972,7 +27802,7 @@
         <v>189</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="C191" s="5" t="s">
         <v>460</v>
@@ -27984,10 +27814,10 @@
         <v>33207</v>
       </c>
       <c r="F191" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G191" s="5" t="s">
-        <v>1154</v>
+        <v>1134</v>
       </c>
       <c r="H191" s="7">
         <v>886190961</v>
@@ -27998,7 +27828,7 @@
         <v>190</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="C192" s="5" t="s">
         <v>463</v>
@@ -28010,10 +27840,10 @@
         <v>37415</v>
       </c>
       <c r="F192" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G192" s="5" t="s">
-        <v>1155</v>
+        <v>1135</v>
       </c>
       <c r="H192" s="7">
         <v>943704988</v>
@@ -28024,7 +27854,7 @@
         <v>191</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="C193" s="5" t="s">
         <v>466</v>
@@ -28036,10 +27866,10 @@
         <v>31606</v>
       </c>
       <c r="F193" s="10" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G193" s="5" t="s">
-        <v>1156</v>
+        <v>1136</v>
       </c>
       <c r="H193" s="7">
         <v>845885078</v>
@@ -28050,7 +27880,7 @@
         <v>192</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="C194" s="5" t="s">
         <v>469</v>
@@ -28062,10 +27892,10 @@
         <v>33284</v>
       </c>
       <c r="F194" s="10" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G194" s="5" t="s">
-        <v>1157</v>
+        <v>1137</v>
       </c>
       <c r="H194" s="7">
         <v>813331991</v>
@@ -28076,7 +27906,7 @@
         <v>193</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="C195" s="5" t="s">
         <v>472</v>
@@ -28088,10 +27918,10 @@
         <v>25063</v>
       </c>
       <c r="F195" s="10" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G195" s="5" t="s">
-        <v>1158</v>
+        <v>1138</v>
       </c>
       <c r="H195" s="7">
         <v>918547379</v>
@@ -28102,7 +27932,7 @@
         <v>194</v>
       </c>
       <c r="B196" s="8" t="s">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="C196" s="8" t="s">
         <v>475</v>
@@ -28114,10 +27944,10 @@
         <v>36973</v>
       </c>
       <c r="F196" s="11" t="s">
-        <v>926</v>
+        <v>906</v>
       </c>
       <c r="G196" s="8" t="s">
-        <v>1159</v>
+        <v>1139</v>
       </c>
       <c r="H196" s="12">
         <v>886144486</v>
@@ -28128,7 +27958,7 @@
         <v>195</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="C197" s="5" t="s">
         <v>478</v>
@@ -28140,10 +27970,10 @@
         <v>32280</v>
       </c>
       <c r="F197" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G197" s="5" t="s">
-        <v>1160</v>
+        <v>1140</v>
       </c>
       <c r="H197" s="7">
         <v>919753029</v>
@@ -28154,7 +27984,7 @@
         <v>196</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="C198" s="5" t="s">
         <v>481</v>
@@ -28166,10 +27996,10 @@
         <v>33576</v>
       </c>
       <c r="F198" s="10" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="G198" s="5" t="s">
-        <v>1161</v>
+        <v>1141</v>
       </c>
       <c r="H198" s="7">
         <v>917359606</v>
@@ -28180,7 +28010,7 @@
         <v>197</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="C199" s="5" t="s">
         <v>511</v>
@@ -28192,10 +28022,10 @@
         <v>30230</v>
       </c>
       <c r="F199" s="10" t="s">
-        <v>1024</v>
+        <v>1004</v>
       </c>
       <c r="G199" s="5" t="s">
-        <v>1162</v>
+        <v>1142</v>
       </c>
       <c r="H199" s="7">
         <v>912039246</v>
@@ -28206,7 +28036,7 @@
         <v>198</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>1036</v>
+        <v>1016</v>
       </c>
       <c r="C200" s="5" t="s">
         <v>569</v>
@@ -28218,10 +28048,10 @@
         <v>35303</v>
       </c>
       <c r="F200" s="10" t="s">
-        <v>1024</v>
+        <v>1004</v>
       </c>
       <c r="G200" s="5" t="s">
-        <v>1163</v>
+        <v>1143</v>
       </c>
       <c r="H200" s="7">
         <v>888068410</v>
@@ -28232,7 +28062,7 @@
         <v>199</v>
       </c>
       <c r="B201" s="13" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="C201" s="13" t="s">
         <v>44</v>
@@ -28244,10 +28074,10 @@
         <v>28716</v>
       </c>
       <c r="F201" s="11" t="s">
-        <v>1062</v>
+        <v>1042</v>
       </c>
       <c r="G201" s="13" t="s">
-        <v>1164</v>
+        <v>1144</v>
       </c>
       <c r="H201" s="15">
         <v>911535088</v>

--- a/chamcong.xlsx
+++ b/chamcong.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmcvnpt-my.sharepoint.com/personal/phuongvl_vpc_vnpt_vn/Documents/AI/1chamcong/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{A8042E9A-3F5C-4731-9B41-1212C11F6FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{973A4DF6-51BC-464A-9701-273F1E1728F1}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{A8042E9A-3F5C-4731-9B41-1212C11F6FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46464A93-9F8C-4927-9956-B43183C80810}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6387" uniqueCount="1145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6351" uniqueCount="1126">
   <si>
     <t>TT</t>
   </si>
@@ -1817,63 +1817,6 @@
   </si>
   <si>
     <t>Nghỉ bù</t>
-  </si>
-  <si>
-    <t>X1/H1</t>
-  </si>
-  <si>
-    <t>Làm ca sáng (6h), chiều học/họp hoặc sáng học/họp, chiều làm</t>
-  </si>
-  <si>
-    <t>H1/X1</t>
-  </si>
-  <si>
-    <t>H1/X2</t>
-  </si>
-  <si>
-    <t>Làm ca sáng (7h), chiều học/họp hoặc sáng học/họp, chiều làm</t>
-  </si>
-  <si>
-    <t>X2/H1</t>
-  </si>
-  <si>
-    <t>X3/H1</t>
-  </si>
-  <si>
-    <t>Làm đêm và học/họp hoặc sáng học/họp, tối làm đêm</t>
-  </si>
-  <si>
-    <t>H1/X3</t>
-  </si>
-  <si>
-    <t>H1/X4</t>
-  </si>
-  <si>
-    <t>X4/H1</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>Đi học, tập huấn, hội nghị</t>
-  </si>
-  <si>
-    <t>H1</t>
-  </si>
-  <si>
-    <t>Học/Họp 4h</t>
-  </si>
-  <si>
-    <t>X/P</t>
-  </si>
-  <si>
-    <t>Làm sáng,chiều nghỉ phép</t>
-  </si>
-  <si>
-    <t>CĐ</t>
-  </si>
-  <si>
-    <t>Nghỉ chế độ</t>
   </si>
   <si>
     <t>Ốm</t>
@@ -4039,16 +3982,16 @@
   <sheetData>
     <row r="1" spans="1:35" ht="28" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>888</v>
+        <v>869</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>889</v>
+        <v>870</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>890</v>
+        <v>871</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>891</v>
+        <v>872</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -21116,7 +21059,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6080A41B-F989-4DD2-B967-3264220228D5}">
-  <dimension ref="A1:C158"/>
+  <dimension ref="A1:C146"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="21.08984375" customWidth="1"/>
@@ -21177,31 +21120,31 @@
         <v>592</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="42" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="C6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="42" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="42" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>596</v>
@@ -21210,1654 +21153,1522 @@
         <v>597</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="42" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>598</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="42" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="42" x14ac:dyDescent="0.35">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="42" x14ac:dyDescent="0.35">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="42" x14ac:dyDescent="0.35">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>22</v>
+        <v>103</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>23</v>
+        <v>106</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>26</v>
+        <v>115</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>43</v>
+        <v>616</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>30</v>
+        <v>128</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="42" x14ac:dyDescent="0.35">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>658</v>
+        <v>597</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>165</v>
+        <v>201</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>177</v>
+        <v>213</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>180</v>
+        <v>216</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>183</v>
+        <v>219</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>198</v>
+        <v>234</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>210</v>
+        <v>246</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>213</v>
+        <v>249</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>222</v>
+        <v>258</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="42" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="56" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>231</v>
+        <v>267</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>234</v>
+        <v>270</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>237</v>
+        <v>273</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>243</v>
+        <v>279</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>246</v>
+        <v>282</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>249</v>
+        <v>285</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>252</v>
+        <v>288</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>261</v>
+        <v>297</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" ht="42" x14ac:dyDescent="0.35">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="56" x14ac:dyDescent="0.35">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>270</v>
+        <v>306</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>273</v>
+        <v>309</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>276</v>
+        <v>312</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>279</v>
+        <v>315</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
-        <v>285</v>
+        <v>321</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>288</v>
+        <v>324</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
-        <v>291</v>
+        <v>327</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>294</v>
+        <v>330</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>297</v>
+        <v>333</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>300</v>
+        <v>336</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>303</v>
+        <v>339</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>309</v>
+        <v>345</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>312</v>
+        <v>348</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>315</v>
+        <v>351</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>327</v>
+        <v>363</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>333</v>
+        <v>368</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>336</v>
+        <v>371</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>339</v>
+        <v>375</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>345</v>
+        <v>381</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>348</v>
+        <v>384</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>357</v>
+        <v>393</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>360</v>
+        <v>396</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>363</v>
+        <v>399</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>366</v>
+        <v>402</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>375</v>
+        <v>411</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>378</v>
+        <v>414</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>381</v>
+        <v>417</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>384</v>
+        <v>420</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>390</v>
+        <v>426</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
-        <v>393</v>
+        <v>429</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
-        <v>396</v>
+        <v>432</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
-        <v>399</v>
+        <v>435</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
-        <v>402</v>
+        <v>438</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
-        <v>405</v>
+        <v>441</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
-        <v>408</v>
+        <v>444</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
-        <v>411</v>
+        <v>447</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
-        <v>414</v>
+        <v>450</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
-        <v>417</v>
+        <v>453</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
-        <v>423</v>
+        <v>459</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
-        <v>426</v>
+        <v>462</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="42" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
-        <v>429</v>
+        <v>465</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" ht="28" x14ac:dyDescent="0.35">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
-        <v>432</v>
+        <v>468</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
-        <v>438</v>
+        <v>474</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="28" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
-        <v>441</v>
+        <v>477</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
-        <v>444</v>
+        <v>480</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
-        <v>447</v>
+        <v>483</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
-        <v>450</v>
+        <v>486</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>853</v>
+        <v>374</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
-        <v>453</v>
+        <v>489</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
-        <v>456</v>
+        <v>492</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
-        <v>459</v>
+        <v>495</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
-        <v>462</v>
+        <v>498</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" ht="42" x14ac:dyDescent="0.35">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
-        <v>465</v>
+        <v>501</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
-        <v>468</v>
+        <v>504</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" ht="28" x14ac:dyDescent="0.35">
-      <c r="A147" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>865</v>
-      </c>
-      <c r="C147" s="3" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" ht="28" x14ac:dyDescent="0.35">
-      <c r="A148" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>867</v>
-      </c>
-      <c r="C148" s="3" t="s">
         <v>868</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" ht="28" x14ac:dyDescent="0.35">
-      <c r="A149" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>869</v>
-      </c>
-      <c r="C149" s="3" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A150" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>871</v>
-      </c>
-      <c r="C150" s="3" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A151" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>873</v>
-      </c>
-      <c r="C151" s="3" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A152" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C152" s="3" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A153" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>876</v>
-      </c>
-      <c r="C153" s="3" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A154" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>878</v>
-      </c>
-      <c r="C154" s="3" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A155" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>880</v>
-      </c>
-      <c r="C155" s="3" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A156" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>882</v>
-      </c>
-      <c r="C156" s="3" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A157" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>884</v>
-      </c>
-      <c r="C157" s="3" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A158" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>886</v>
-      </c>
-      <c r="C158" s="3" t="s">
-        <v>887</v>
       </c>
     </row>
   </sheetData>
@@ -22875,28 +22686,28 @@
   <sheetData>
     <row r="1" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>888</v>
+        <v>869</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>892</v>
+        <v>873</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>893</v>
+        <v>874</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>894</v>
+        <v>875</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>895</v>
+        <v>876</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>896</v>
+        <v>877</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>897</v>
+        <v>878</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>898</v>
+        <v>879</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -22914,7 +22725,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>899</v>
+        <v>880</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>32</v>
@@ -22926,10 +22737,10 @@
         <v>29698</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>900</v>
+        <v>881</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>901</v>
+        <v>882</v>
       </c>
       <c r="H3" s="7">
         <v>912222493</v>
@@ -22940,7 +22751,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>899</v>
+        <v>880</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>35</v>
@@ -22952,10 +22763,10 @@
         <v>30356</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>902</v>
+        <v>883</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>903</v>
+        <v>884</v>
       </c>
       <c r="H4" s="7">
         <v>913282346</v>
@@ -22966,7 +22777,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>899</v>
+        <v>880</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>37</v>
@@ -22978,10 +22789,10 @@
         <v>27992</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>902</v>
+        <v>883</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>904</v>
+        <v>885</v>
       </c>
       <c r="H5" s="7">
         <v>912026525</v>
@@ -22992,7 +22803,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>82</v>
@@ -23004,10 +22815,10 @@
         <v>29928</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>906</v>
+        <v>887</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>907</v>
+        <v>888</v>
       </c>
       <c r="H6" s="7">
         <v>915225103</v>
@@ -23018,7 +22829,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>85</v>
@@ -23030,10 +22841,10 @@
         <v>27060</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>909</v>
+        <v>890</v>
       </c>
       <c r="H7" s="7">
         <v>912664497</v>
@@ -23044,7 +22855,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>87</v>
@@ -23056,10 +22867,10 @@
         <v>29397</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>910</v>
+        <v>891</v>
       </c>
       <c r="H8" s="7">
         <v>912550789</v>
@@ -23070,7 +22881,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>89</v>
@@ -23082,10 +22893,10 @@
         <v>28689</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>906</v>
+        <v>887</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>911</v>
+        <v>892</v>
       </c>
       <c r="H9" s="7">
         <v>916167717</v>
@@ -23096,7 +22907,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>91</v>
@@ -23108,10 +22919,10 @@
         <v>32221</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>912</v>
+        <v>893</v>
       </c>
       <c r="H10" s="7">
         <v>917238588</v>
@@ -23122,7 +22933,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>93</v>
@@ -23134,10 +22945,10 @@
         <v>28546</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>913</v>
+        <v>894</v>
       </c>
       <c r="H11" s="7">
         <v>912247005</v>
@@ -23148,7 +22959,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>95</v>
@@ -23160,10 +22971,10 @@
         <v>28421</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>914</v>
+        <v>895</v>
       </c>
       <c r="H12" s="7">
         <v>813697799</v>
@@ -23174,7 +22985,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>98</v>
@@ -23186,10 +22997,10 @@
         <v>31293</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>915</v>
+        <v>896</v>
       </c>
       <c r="H13" s="7">
         <v>946066699</v>
@@ -23200,7 +23011,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>101</v>
@@ -23212,10 +23023,10 @@
         <v>30032</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>916</v>
+        <v>897</v>
       </c>
       <c r="H14" s="7">
         <v>919782286</v>
@@ -23226,7 +23037,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>104</v>
@@ -23238,10 +23049,10 @@
         <v>30948</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>917</v>
+        <v>898</v>
       </c>
       <c r="H15" s="7">
         <v>915773888</v>
@@ -23252,7 +23063,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>107</v>
@@ -23264,10 +23075,10 @@
         <v>30401</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>918</v>
+        <v>899</v>
       </c>
       <c r="H16" s="7">
         <v>915030165</v>
@@ -23278,7 +23089,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>110</v>
@@ -23290,10 +23101,10 @@
         <v>32479</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>919</v>
+        <v>900</v>
       </c>
       <c r="H17" s="7">
         <v>912640246</v>
@@ -23304,7 +23115,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>113</v>
@@ -23316,10 +23127,10 @@
         <v>31367</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>920</v>
+        <v>901</v>
       </c>
       <c r="H18" s="7">
         <v>941125125</v>
@@ -23330,7 +23141,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>116</v>
@@ -23342,10 +23153,10 @@
         <v>27629</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>921</v>
+        <v>902</v>
       </c>
       <c r="H19" s="7">
         <v>912259244</v>
@@ -23356,7 +23167,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>119</v>
@@ -23368,10 +23179,10 @@
         <v>33166</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>922</v>
+        <v>903</v>
       </c>
       <c r="H20" s="7">
         <v>911639191</v>
@@ -23382,7 +23193,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>122</v>
@@ -23394,10 +23205,10 @@
         <v>32119</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>923</v>
+        <v>904</v>
       </c>
       <c r="H21" s="7">
         <v>911111987</v>
@@ -23408,7 +23219,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>126</v>
@@ -23420,10 +23231,10 @@
         <v>27021</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>924</v>
+        <v>905</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>925</v>
+        <v>906</v>
       </c>
       <c r="H22" s="7">
         <v>913261808</v>
@@ -23434,7 +23245,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>926</v>
+        <v>907</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>141</v>
@@ -23446,10 +23257,10 @@
         <v>28126</v>
       </c>
       <c r="F23" s="5" t="s">
+        <v>889</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>908</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>927</v>
       </c>
       <c r="H23" s="7">
         <v>917035444</v>
@@ -23460,7 +23271,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>926</v>
+        <v>907</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>144</v>
@@ -23472,10 +23283,10 @@
         <v>32953</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>928</v>
+        <v>909</v>
       </c>
       <c r="H24" s="7">
         <v>911232324</v>
@@ -23486,7 +23297,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>926</v>
+        <v>907</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>148</v>
@@ -23498,10 +23309,10 @@
         <v>27669</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>929</v>
+        <v>910</v>
       </c>
       <c r="H25" s="7">
         <v>918153188</v>
@@ -23512,7 +23323,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>926</v>
+        <v>907</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>151</v>
@@ -23524,10 +23335,10 @@
         <v>26388</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>924</v>
+        <v>905</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>930</v>
+        <v>911</v>
       </c>
       <c r="H26" s="7">
         <v>916167929</v>
@@ -23538,7 +23349,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>931</v>
+        <v>912</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>166</v>
@@ -23550,10 +23361,10 @@
         <v>26782</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>906</v>
+        <v>887</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>932</v>
+        <v>913</v>
       </c>
       <c r="H27" s="7">
         <v>912338586</v>
@@ -23564,7 +23375,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>931</v>
+        <v>912</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>169</v>
@@ -23576,10 +23387,10 @@
         <v>27985</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>933</v>
+        <v>914</v>
       </c>
       <c r="H28" s="7">
         <v>912110176</v>
@@ -23590,7 +23401,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>931</v>
+        <v>912</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>172</v>
@@ -23602,10 +23413,10 @@
         <v>33713</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>934</v>
+        <v>915</v>
       </c>
       <c r="H29" s="7">
         <v>911122338</v>
@@ -23616,7 +23427,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>931</v>
+        <v>912</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>175</v>
@@ -23628,10 +23439,10 @@
         <v>31967</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>935</v>
+        <v>916</v>
       </c>
       <c r="H30" s="7">
         <v>915047773</v>
@@ -23642,7 +23453,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>931</v>
+        <v>912</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>178</v>
@@ -23654,10 +23465,10 @@
         <v>27880</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>936</v>
+        <v>917</v>
       </c>
       <c r="H31" s="7">
         <v>915773848</v>
@@ -23668,7 +23479,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>931</v>
+        <v>912</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>181</v>
@@ -23680,10 +23491,10 @@
         <v>29389</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>924</v>
+        <v>905</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>937</v>
+        <v>918</v>
       </c>
       <c r="H32" s="7">
         <v>913170680</v>
@@ -23694,7 +23505,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>931</v>
+        <v>912</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>184</v>
@@ -23706,10 +23517,10 @@
         <v>27581</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>924</v>
+        <v>905</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>938</v>
+        <v>919</v>
       </c>
       <c r="H33" s="7">
         <v>917968768</v>
@@ -23720,7 +23531,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>939</v>
+        <v>920</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>202</v>
@@ -23732,10 +23543,10 @@
         <v>31560</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>941</v>
+        <v>922</v>
       </c>
       <c r="H34" s="7">
         <v>917161767</v>
@@ -23746,7 +23557,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>939</v>
+        <v>920</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>205</v>
@@ -23758,10 +23569,10 @@
         <v>33130</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>942</v>
+        <v>923</v>
       </c>
       <c r="H35" s="7">
         <v>916867200</v>
@@ -23772,7 +23583,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>939</v>
+        <v>920</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>208</v>
@@ -23784,10 +23595,10 @@
         <v>29048</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>943</v>
+        <v>924</v>
       </c>
       <c r="H36" s="7">
         <v>912913305</v>
@@ -23798,7 +23609,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>939</v>
+        <v>920</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>211</v>
@@ -23810,10 +23621,10 @@
         <v>26750</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>944</v>
+        <v>925</v>
       </c>
       <c r="H37" s="7">
         <v>836569888</v>
@@ -23824,7 +23635,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>939</v>
+        <v>920</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>214</v>
@@ -23836,10 +23647,10 @@
         <v>32282</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>945</v>
+        <v>926</v>
       </c>
       <c r="H38" s="7">
         <v>918701988</v>
@@ -23850,7 +23661,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>939</v>
+        <v>920</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>217</v>
@@ -23862,10 +23673,10 @@
         <v>30895</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>946</v>
+        <v>927</v>
       </c>
       <c r="H39" s="7">
         <v>912465450</v>
@@ -23876,7 +23687,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>939</v>
+        <v>920</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>220</v>
@@ -23888,10 +23699,10 @@
         <v>31280</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>947</v>
+        <v>928</v>
       </c>
       <c r="H40" s="7">
         <v>946221885</v>
@@ -23902,7 +23713,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>939</v>
+        <v>920</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>223</v>
@@ -23914,10 +23725,10 @@
         <v>29888</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>924</v>
+        <v>905</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>948</v>
+        <v>929</v>
       </c>
       <c r="H41" s="7">
         <v>913096338</v>
@@ -23928,7 +23739,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>262</v>
@@ -23940,10 +23751,10 @@
         <v>26924</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>906</v>
+        <v>887</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>950</v>
+        <v>931</v>
       </c>
       <c r="H42" s="7">
         <v>918551138</v>
@@ -23954,7 +23765,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>265</v>
@@ -23966,10 +23777,10 @@
         <v>27361</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>951</v>
+        <v>932</v>
       </c>
       <c r="H43" s="7">
         <v>917867966</v>
@@ -23980,7 +23791,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>268</v>
@@ -23992,10 +23803,10 @@
         <v>32013</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>952</v>
+        <v>933</v>
       </c>
       <c r="H44" s="7">
         <v>946044333</v>
@@ -24006,7 +23817,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>271</v>
@@ -24018,10 +23829,10 @@
         <v>29646</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>906</v>
+        <v>887</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>953</v>
+        <v>934</v>
       </c>
       <c r="H45" s="7">
         <v>948313222</v>
@@ -24032,7 +23843,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>274</v>
@@ -24044,10 +23855,10 @@
         <v>29435</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>906</v>
+        <v>887</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>954</v>
+        <v>935</v>
       </c>
       <c r="H46" s="7">
         <v>913338091</v>
@@ -24058,7 +23869,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>277</v>
@@ -24070,10 +23881,10 @@
         <v>30415</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>924</v>
+        <v>905</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>955</v>
+        <v>936</v>
       </c>
       <c r="H47" s="7">
         <v>912188383</v>
@@ -24084,7 +23895,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>956</v>
+        <v>937</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>292</v>
@@ -24096,10 +23907,10 @@
         <v>27020</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>957</v>
+        <v>938</v>
       </c>
       <c r="H48" s="7">
         <v>915275186</v>
@@ -24110,7 +23921,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>956</v>
+        <v>937</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>295</v>
@@ -24122,10 +23933,10 @@
         <v>31554</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>958</v>
+        <v>939</v>
       </c>
       <c r="H49" s="7">
         <v>915921123</v>
@@ -24136,7 +23947,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>956</v>
+        <v>937</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>298</v>
@@ -24148,10 +23959,10 @@
         <v>30318</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>959</v>
+        <v>940</v>
       </c>
       <c r="H50" s="7">
         <v>838343366</v>
@@ -24162,7 +23973,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>956</v>
+        <v>937</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>301</v>
@@ -24174,10 +23985,10 @@
         <v>26600</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>960</v>
+        <v>941</v>
       </c>
       <c r="H51" s="7">
         <v>912957533</v>
@@ -24188,7 +23999,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>956</v>
+        <v>937</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>304</v>
@@ -24200,10 +24011,10 @@
         <v>29792</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>961</v>
+        <v>942</v>
       </c>
       <c r="H52" s="7">
         <v>916085707</v>
@@ -24214,7 +24025,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>956</v>
+        <v>937</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>307</v>
@@ -24226,10 +24037,10 @@
         <v>30695</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>962</v>
+        <v>943</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>963</v>
+        <v>944</v>
       </c>
       <c r="H53" s="7">
         <v>919154686</v>
@@ -24240,7 +24051,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>956</v>
+        <v>937</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>310</v>
@@ -24252,10 +24063,10 @@
         <v>31036</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>924</v>
+        <v>905</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>964</v>
+        <v>945</v>
       </c>
       <c r="H54" s="7">
         <v>944834000</v>
@@ -24266,7 +24077,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>337</v>
@@ -24278,10 +24089,10 @@
         <v>34221</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>966</v>
+        <v>947</v>
       </c>
       <c r="H55" s="7">
         <v>814177686</v>
@@ -24292,7 +24103,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>340</v>
@@ -24304,10 +24115,10 @@
         <v>29443</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>967</v>
+        <v>948</v>
       </c>
       <c r="H56" s="7">
         <v>915834000</v>
@@ -24318,7 +24129,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>343</v>
@@ -24330,10 +24141,10 @@
         <v>31979</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>968</v>
+        <v>949</v>
       </c>
       <c r="H57" s="7">
         <v>916621787</v>
@@ -24344,7 +24155,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>346</v>
@@ -24356,10 +24167,10 @@
         <v>28542</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>969</v>
+        <v>950</v>
       </c>
       <c r="H58" s="7">
         <v>913504171</v>
@@ -24370,7 +24181,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>349</v>
@@ -24382,10 +24193,10 @@
         <v>30185</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>970</v>
+        <v>951</v>
       </c>
       <c r="H59" s="7">
         <v>915220882</v>
@@ -24396,7 +24207,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>352</v>
@@ -24408,10 +24219,10 @@
         <v>28136</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>971</v>
+        <v>952</v>
       </c>
       <c r="H60" s="7">
         <v>919682692</v>
@@ -24422,7 +24233,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>355</v>
@@ -24434,10 +24245,10 @@
         <v>31701</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>924</v>
+        <v>905</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>972</v>
+        <v>953</v>
       </c>
       <c r="H61" s="7">
         <v>912991988</v>
@@ -24448,7 +24259,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>973</v>
+        <v>954</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>391</v>
@@ -24460,10 +24271,10 @@
         <v>28754</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>974</v>
+        <v>955</v>
       </c>
       <c r="H62" s="7">
         <v>919663111</v>
@@ -24474,7 +24285,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>973</v>
+        <v>954</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>394</v>
@@ -24486,10 +24297,10 @@
         <v>27911</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>975</v>
+        <v>956</v>
       </c>
       <c r="H63" s="7">
         <v>917003681</v>
@@ -24500,7 +24311,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>973</v>
+        <v>954</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>397</v>
@@ -24512,10 +24323,10 @@
         <v>32832</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>976</v>
+        <v>957</v>
       </c>
       <c r="H64" s="7">
         <v>911201189</v>
@@ -24526,7 +24337,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>973</v>
+        <v>954</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>400</v>
@@ -24538,10 +24349,10 @@
         <v>31936</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>977</v>
+        <v>958</v>
       </c>
       <c r="H65" s="7">
         <v>919080687</v>
@@ -24552,7 +24363,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>973</v>
+        <v>954</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>403</v>
@@ -24564,10 +24375,10 @@
         <v>31659</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>924</v>
+        <v>905</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>978</v>
+        <v>959</v>
       </c>
       <c r="H66" s="7">
         <v>833365333</v>
@@ -24578,7 +24389,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>979</v>
+        <v>960</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>418</v>
@@ -24590,10 +24401,10 @@
         <v>28907</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>980</v>
+        <v>961</v>
       </c>
       <c r="H67" s="7">
         <v>916993000</v>
@@ -24604,7 +24415,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>979</v>
+        <v>960</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>421</v>
@@ -24616,10 +24427,10 @@
         <v>29951</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>981</v>
+        <v>962</v>
       </c>
       <c r="H68" s="7">
         <v>916638668</v>
@@ -24630,7 +24441,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>979</v>
+        <v>960</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>424</v>
@@ -24642,10 +24453,10 @@
         <v>30136</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>982</v>
+        <v>963</v>
       </c>
       <c r="H69" s="7">
         <v>912980266</v>
@@ -24656,7 +24467,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>979</v>
+        <v>960</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>427</v>
@@ -24668,10 +24479,10 @@
         <v>31992</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>983</v>
+        <v>964</v>
       </c>
       <c r="H70" s="7">
         <v>913282195</v>
@@ -24682,7 +24493,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>979</v>
+        <v>960</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>430</v>
@@ -24694,10 +24505,10 @@
         <v>31065</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>984</v>
+        <v>965</v>
       </c>
       <c r="H71" s="7">
         <v>912964696</v>
@@ -24708,7 +24519,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>979</v>
+        <v>960</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>433</v>
@@ -24720,10 +24531,10 @@
         <v>28836</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>985</v>
+        <v>966</v>
       </c>
       <c r="H72" s="7">
         <v>916084558</v>
@@ -24734,7 +24545,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>979</v>
+        <v>960</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>436</v>
@@ -24746,10 +24557,10 @@
         <v>29883</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>986</v>
+        <v>967</v>
       </c>
       <c r="H73" s="7">
         <v>914012626</v>
@@ -24760,7 +24571,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>979</v>
+        <v>960</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>439</v>
@@ -24772,10 +24583,10 @@
         <v>28977</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>987</v>
+        <v>968</v>
       </c>
       <c r="H74" s="7">
         <v>942904222</v>
@@ -24786,7 +24597,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>979</v>
+        <v>960</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>442</v>
@@ -24798,10 +24609,10 @@
         <v>31081</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>988</v>
+        <v>969</v>
       </c>
       <c r="H75" s="7">
         <v>916313368</v>
@@ -24812,7 +24623,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>979</v>
+        <v>960</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>445</v>
@@ -24824,10 +24635,10 @@
         <v>28783</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>989</v>
+        <v>970</v>
       </c>
       <c r="H76" s="7">
         <v>947545777</v>
@@ -24838,7 +24649,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>979</v>
+        <v>960</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>448</v>
@@ -24850,10 +24661,10 @@
         <v>28793</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>990</v>
+        <v>971</v>
       </c>
       <c r="H77" s="7">
         <v>912776868</v>
@@ -24864,7 +24675,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>979</v>
+        <v>960</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>451</v>
@@ -24876,10 +24687,10 @@
         <v>31515</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>906</v>
+        <v>887</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>991</v>
+        <v>972</v>
       </c>
       <c r="H78" s="7">
         <v>945130486</v>
@@ -24890,7 +24701,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>979</v>
+        <v>960</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>454</v>
@@ -24902,10 +24713,10 @@
         <v>29146</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>924</v>
+        <v>905</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>992</v>
+        <v>973</v>
       </c>
       <c r="H79" s="7">
         <v>913389699</v>
@@ -24916,7 +24727,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>484</v>
@@ -24928,10 +24739,10 @@
         <v>31166</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>994</v>
+        <v>975</v>
       </c>
       <c r="H80" s="7">
         <v>918013222</v>
@@ -24942,7 +24753,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>487</v>
@@ -24954,10 +24765,10 @@
         <v>26535</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>995</v>
+        <v>976</v>
       </c>
       <c r="H81" s="7">
         <v>912201468</v>
@@ -24968,7 +24779,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>490</v>
@@ -24980,10 +24791,10 @@
         <v>29957</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>996</v>
+        <v>977</v>
       </c>
       <c r="H82" s="7">
         <v>825161357</v>
@@ -24994,7 +24805,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>493</v>
@@ -25006,10 +24817,10 @@
         <v>26461</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>997</v>
+        <v>978</v>
       </c>
       <c r="H83" s="7">
         <v>913244267</v>
@@ -25020,7 +24831,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>496</v>
@@ -25032,10 +24843,10 @@
         <v>28884</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>906</v>
+        <v>887</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>998</v>
+        <v>979</v>
       </c>
       <c r="H84" s="7">
         <v>946716699</v>
@@ -25046,7 +24857,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>499</v>
@@ -25058,10 +24869,10 @@
         <v>30935</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>999</v>
+        <v>980</v>
       </c>
       <c r="H85" s="7">
         <v>943074777</v>
@@ -25072,7 +24883,7 @@
         <v>84</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>502</v>
@@ -25084,10 +24895,10 @@
         <v>32187</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>906</v>
+        <v>887</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>1000</v>
+        <v>981</v>
       </c>
       <c r="H86" s="7">
         <v>943307007</v>
@@ -25098,7 +24909,7 @@
         <v>85</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>505</v>
@@ -25110,10 +24921,10 @@
         <v>32448</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>1001</v>
+        <v>982</v>
       </c>
       <c r="H87" s="7">
         <v>913339683</v>
@@ -25124,7 +24935,7 @@
         <v>86</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>508</v>
@@ -25136,10 +24947,10 @@
         <v>30198</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>924</v>
+        <v>905</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>1002</v>
+        <v>983</v>
       </c>
       <c r="H88" s="7">
         <v>945116677</v>
@@ -25150,7 +24961,7 @@
         <v>87</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>1003</v>
+        <v>984</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>578</v>
@@ -25162,10 +24973,10 @@
         <v>30738</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>1004</v>
+        <v>985</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>1005</v>
+        <v>986</v>
       </c>
       <c r="H89" s="7">
         <v>916851355</v>
@@ -25176,7 +24987,7 @@
         <v>88</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>1003</v>
+        <v>984</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>580</v>
@@ -25188,10 +24999,10 @@
         <v>31759</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>1004</v>
+        <v>985</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>1006</v>
+        <v>987</v>
       </c>
       <c r="H90" s="7">
         <v>915555452</v>
@@ -25202,7 +25013,7 @@
         <v>89</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>1003</v>
+        <v>984</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>582</v>
@@ -25214,10 +25025,10 @@
         <v>29859</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>1004</v>
+        <v>985</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>1007</v>
+        <v>988</v>
       </c>
       <c r="H91" s="7">
         <v>915773775</v>
@@ -25228,7 +25039,7 @@
         <v>90</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>1003</v>
+        <v>984</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>585</v>
@@ -25240,10 +25051,10 @@
         <v>29102</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>1008</v>
+        <v>989</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>1009</v>
+        <v>990</v>
       </c>
       <c r="H92" s="7">
         <v>913296045</v>
@@ -25254,7 +25065,7 @@
         <v>91</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>1010</v>
+        <v>991</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>514</v>
@@ -25266,10 +25077,10 @@
         <v>30317</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>1004</v>
+        <v>985</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>1011</v>
+        <v>992</v>
       </c>
       <c r="H93" s="7">
         <v>913849865</v>
@@ -25280,7 +25091,7 @@
         <v>92</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>1010</v>
+        <v>991</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>517</v>
@@ -25292,10 +25103,10 @@
         <v>30963</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>1004</v>
+        <v>985</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>1012</v>
+        <v>993</v>
       </c>
       <c r="H94" s="7">
         <v>888222886</v>
@@ -25306,7 +25117,7 @@
         <v>93</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>1010</v>
+        <v>991</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>519</v>
@@ -25318,10 +25129,10 @@
         <v>35675</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>1004</v>
+        <v>985</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>1013</v>
+        <v>994</v>
       </c>
       <c r="H95" s="7">
         <v>943591997</v>
@@ -25332,7 +25143,7 @@
         <v>94</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>1010</v>
+        <v>991</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>522</v>
@@ -25344,10 +25155,10 @@
         <v>32362</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>1004</v>
+        <v>985</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>1014</v>
+        <v>995</v>
       </c>
       <c r="H96" s="7">
         <v>949844489</v>
@@ -25358,7 +25169,7 @@
         <v>95</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>1010</v>
+        <v>991</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>525</v>
@@ -25370,10 +25181,10 @@
         <v>34155</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>1008</v>
+        <v>989</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>1015</v>
+        <v>996</v>
       </c>
       <c r="H97" s="7">
         <v>941068993</v>
@@ -25384,7 +25195,7 @@
         <v>96</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>1016</v>
+        <v>997</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>572</v>
@@ -25396,10 +25207,10 @@
         <v>33010</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>1004</v>
+        <v>985</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>1017</v>
+        <v>998</v>
       </c>
       <c r="H98" s="7">
         <v>911486686</v>
@@ -25410,7 +25221,7 @@
         <v>97</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>1016</v>
+        <v>997</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>575</v>
@@ -25422,10 +25233,10 @@
         <v>32772</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>1008</v>
+        <v>989</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>1018</v>
+        <v>999</v>
       </c>
       <c r="H99" s="7">
         <v>913183089</v>
@@ -25436,7 +25247,7 @@
         <v>98</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>1019</v>
+        <v>1000</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>528</v>
@@ -25448,10 +25259,10 @@
         <v>30061</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>1020</v>
+        <v>1001</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>1021</v>
+        <v>1002</v>
       </c>
       <c r="H100" s="7">
         <v>942466222</v>
@@ -25462,7 +25273,7 @@
         <v>99</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>1019</v>
+        <v>1000</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>531</v>
@@ -25474,10 +25285,10 @@
         <v>35146</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>1020</v>
+        <v>1001</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>1022</v>
+        <v>1003</v>
       </c>
       <c r="H101" s="7">
         <v>888360396</v>
@@ -25488,7 +25299,7 @@
         <v>100</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>1019</v>
+        <v>1000</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>534</v>
@@ -25500,10 +25311,10 @@
         <v>32643</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>1020</v>
+        <v>1001</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>1023</v>
+        <v>1004</v>
       </c>
       <c r="H102" s="7">
         <v>911244989</v>
@@ -25514,7 +25325,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>1019</v>
+        <v>1000</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>39</v>
@@ -25526,10 +25337,10 @@
         <v>29910</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>1024</v>
+        <v>1005</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>1025</v>
+        <v>1006</v>
       </c>
       <c r="H103" s="7">
         <v>912634868</v>
@@ -25540,7 +25351,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>1019</v>
+        <v>1000</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>540</v>
@@ -25552,10 +25363,10 @@
         <v>30578</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>1026</v>
+        <v>1007</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>1027</v>
+        <v>1008</v>
       </c>
       <c r="H104" s="7">
         <v>942271189</v>
@@ -25566,7 +25377,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>1019</v>
+        <v>1000</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>537</v>
@@ -25578,10 +25389,10 @@
         <v>32061</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>1026</v>
+        <v>1007</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>1028</v>
+        <v>1009</v>
       </c>
       <c r="H105" s="7">
         <v>948433188</v>
@@ -25592,7 +25403,7 @@
         <v>104</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>1019</v>
+        <v>1000</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>543</v>
@@ -25604,10 +25415,10 @@
         <v>29801</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>1026</v>
+        <v>1007</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>1029</v>
+        <v>1010</v>
       </c>
       <c r="H106" s="7">
         <v>912777078</v>
@@ -25618,7 +25429,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>1019</v>
+        <v>1000</v>
       </c>
       <c r="C107" s="5" t="s">
         <v>546</v>
@@ -25630,10 +25441,10 @@
         <v>27484</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>1026</v>
+        <v>1007</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>1030</v>
+        <v>1011</v>
       </c>
       <c r="H107" s="7">
         <v>912577679</v>
@@ -25644,7 +25455,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>1019</v>
+        <v>1000</v>
       </c>
       <c r="C108" s="5" t="s">
         <v>549</v>
@@ -25656,10 +25467,10 @@
         <v>34742</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>1026</v>
+        <v>1007</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>1031</v>
+        <v>1012</v>
       </c>
       <c r="H108" s="7">
         <v>913122995</v>
@@ -25670,7 +25481,7 @@
         <v>107</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>1019</v>
+        <v>1000</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>54</v>
@@ -25682,10 +25493,10 @@
         <v>29922</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>1026</v>
+        <v>1007</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>1032</v>
+        <v>1013</v>
       </c>
       <c r="H109" s="7">
         <v>914565181</v>
@@ -25696,7 +25507,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>1019</v>
+        <v>1000</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>552</v>
@@ -25708,10 +25519,10 @@
         <v>29924</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>1026</v>
+        <v>1007</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>1033</v>
+        <v>1014</v>
       </c>
       <c r="H110" s="7">
         <v>914626626</v>
@@ -25722,7 +25533,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>1019</v>
+        <v>1000</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>554</v>
@@ -25734,10 +25545,10 @@
         <v>27839</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>1026</v>
+        <v>1007</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>1034</v>
+        <v>1015</v>
       </c>
       <c r="H111" s="7">
         <v>916840999</v>
@@ -25748,7 +25559,7 @@
         <v>110</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>1019</v>
+        <v>1000</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>557</v>
@@ -25760,10 +25571,10 @@
         <v>34213</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>1026</v>
+        <v>1007</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>1035</v>
+        <v>1016</v>
       </c>
       <c r="H112" s="7">
         <v>912960386</v>
@@ -25774,7 +25585,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>1019</v>
+        <v>1000</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>560</v>
@@ -25786,10 +25597,10 @@
         <v>31071</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>1026</v>
+        <v>1007</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>1036</v>
+        <v>1017</v>
       </c>
       <c r="H113" s="7">
         <v>916360325</v>
@@ -25800,7 +25611,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>1019</v>
+        <v>1000</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>563</v>
@@ -25812,10 +25623,10 @@
         <v>30850</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>1026</v>
+        <v>1007</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>1037</v>
+        <v>1018</v>
       </c>
       <c r="H114" s="7">
         <v>942795027</v>
@@ -25826,7 +25637,7 @@
         <v>113</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>1019</v>
+        <v>1000</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>566</v>
@@ -25838,10 +25649,10 @@
         <v>29015</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>1026</v>
+        <v>1007</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>1038</v>
+        <v>1019</v>
       </c>
       <c r="H115" s="7">
         <v>912581259</v>
@@ -25852,7 +25663,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>41</v>
@@ -25864,10 +25675,10 @@
         <v>29717</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>1040</v>
+        <v>1021</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>1041</v>
+        <v>1022</v>
       </c>
       <c r="H116" s="7">
         <v>911601999</v>
@@ -25878,7 +25689,7 @@
         <v>115</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>46</v>
@@ -25890,10 +25701,10 @@
         <v>30609</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>1042</v>
+        <v>1023</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>1043</v>
+        <v>1024</v>
       </c>
       <c r="H117" s="7">
         <v>918474583</v>
@@ -25904,7 +25715,7 @@
         <v>116</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>48</v>
@@ -25916,10 +25727,10 @@
         <v>29594</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>1042</v>
+        <v>1023</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>1044</v>
+        <v>1025</v>
       </c>
       <c r="H118" s="7">
         <v>913282523</v>
@@ -25930,7 +25741,7 @@
         <v>117</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C119" s="5" t="s">
         <v>50</v>
@@ -25942,10 +25753,10 @@
         <v>25447</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>1045</v>
+        <v>1026</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>1046</v>
+        <v>1027</v>
       </c>
       <c r="H119" s="7">
         <v>913282010</v>
@@ -25956,7 +25767,7 @@
         <v>118</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C120" s="5" t="s">
         <v>52</v>
@@ -25968,10 +25779,10 @@
         <v>29882</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>1047</v>
+        <v>1028</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>1048</v>
+        <v>1029</v>
       </c>
       <c r="H120" s="7">
         <v>915171567</v>
@@ -25982,22 +25793,22 @@
         <v>119</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>1049</v>
+        <v>1030</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>1050</v>
+        <v>1031</v>
       </c>
       <c r="E121" s="6">
         <v>25150</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>1051</v>
+        <v>1032</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>1052</v>
+        <v>1033</v>
       </c>
       <c r="H121" s="7">
         <v>913869189</v>
@@ -26008,22 +25819,22 @@
         <v>120</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>1053</v>
+        <v>1034</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>1054</v>
+        <v>1035</v>
       </c>
       <c r="E122" s="9">
         <v>26605</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>1051</v>
+        <v>1032</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>1055</v>
+        <v>1036</v>
       </c>
       <c r="H122" s="7">
         <v>916466451</v>
@@ -26034,22 +25845,22 @@
         <v>121</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>1056</v>
+        <v>1037</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>1057</v>
+        <v>1038</v>
       </c>
       <c r="E123" s="6">
         <v>27437</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>1051</v>
+        <v>1032</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>1058</v>
+        <v>1039</v>
       </c>
       <c r="H123" s="7">
         <v>913592422</v>
@@ -26060,7 +25871,7 @@
         <v>122</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C124" s="5" t="s">
         <v>56</v>
@@ -26072,10 +25883,10 @@
         <v>30435</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>1047</v>
+        <v>1028</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>1059</v>
+        <v>1040</v>
       </c>
       <c r="H124" s="7">
         <v>918666808</v>
@@ -26086,7 +25897,7 @@
         <v>123</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>58</v>
@@ -26098,10 +25909,10 @@
         <v>28789</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>1042</v>
+        <v>1023</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>1060</v>
+        <v>1041</v>
       </c>
       <c r="H125" s="7">
         <v>918581978</v>
@@ -26112,7 +25923,7 @@
         <v>124</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>60</v>
@@ -26124,10 +25935,10 @@
         <v>28537</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>1061</v>
+        <v>1042</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>1062</v>
+        <v>1043</v>
       </c>
       <c r="H126" s="7">
         <v>943128668</v>
@@ -26138,7 +25949,7 @@
         <v>125</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>62</v>
@@ -26150,10 +25961,10 @@
         <v>29255</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>1063</v>
+        <v>1044</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>1064</v>
+        <v>1045</v>
       </c>
       <c r="H127" s="7">
         <v>945116689</v>
@@ -26164,7 +25975,7 @@
         <v>126</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C128" s="8" t="s">
         <v>64</v>
@@ -26176,10 +25987,10 @@
         <v>31938</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>1047</v>
+        <v>1028</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>1065</v>
+        <v>1046</v>
       </c>
       <c r="H128" s="7">
         <v>912191516</v>
@@ -26190,7 +26001,7 @@
         <v>127</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C129" s="5" t="s">
         <v>66</v>
@@ -26202,10 +26013,10 @@
         <v>29414</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>1063</v>
+        <v>1044</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>1066</v>
+        <v>1047</v>
       </c>
       <c r="H129" s="7">
         <v>947118999</v>
@@ -26216,7 +26027,7 @@
         <v>128</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C130" s="5" t="s">
         <v>68</v>
@@ -26228,10 +26039,10 @@
         <v>28823</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>1042</v>
+        <v>1023</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>1067</v>
+        <v>1048</v>
       </c>
       <c r="H130" s="7">
         <v>912211382</v>
@@ -26242,7 +26053,7 @@
         <v>129</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>70</v>
@@ -26254,10 +26065,10 @@
         <v>32201</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>1061</v>
+        <v>1042</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>1068</v>
+        <v>1049</v>
       </c>
       <c r="H131" s="7">
         <v>948517222</v>
@@ -26268,7 +26079,7 @@
         <v>130</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>72</v>
@@ -26280,10 +26091,10 @@
         <v>27746</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>1042</v>
+        <v>1023</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>1069</v>
+        <v>1050</v>
       </c>
       <c r="H132" s="7">
         <v>912362552</v>
@@ -26294,7 +26105,7 @@
         <v>131</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>74</v>
@@ -26306,10 +26117,10 @@
         <v>28493</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>1047</v>
+        <v>1028</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>1070</v>
+        <v>1051</v>
       </c>
       <c r="H133" s="7">
         <v>914838555</v>
@@ -26320,7 +26131,7 @@
         <v>132</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>76</v>
@@ -26332,10 +26143,10 @@
         <v>27776</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>1063</v>
+        <v>1044</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>1071</v>
+        <v>1052</v>
       </c>
       <c r="H134" s="7">
         <v>915687676</v>
@@ -26346,22 +26157,22 @@
         <v>133</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>1072</v>
+        <v>1053</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>1073</v>
+        <v>1054</v>
       </c>
       <c r="E135" s="6">
         <v>26794</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>1051</v>
+        <v>1032</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>1074</v>
+        <v>1055</v>
       </c>
       <c r="H135" s="7">
         <v>911121973</v>
@@ -26372,22 +26183,22 @@
         <v>134</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>1075</v>
+        <v>1056</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>1076</v>
+        <v>1057</v>
       </c>
       <c r="E136" s="6">
         <v>28415</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>1051</v>
+        <v>1032</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>1077</v>
+        <v>1058</v>
       </c>
       <c r="H136" s="7">
         <v>915893067</v>
@@ -26398,22 +26209,22 @@
         <v>135</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>1078</v>
+        <v>1059</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>1079</v>
+        <v>1060</v>
       </c>
       <c r="E137" s="6">
         <v>26672</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>1051</v>
+        <v>1032</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>1080</v>
+        <v>1061</v>
       </c>
       <c r="H137" s="7">
         <v>918004889</v>
@@ -26424,7 +26235,7 @@
         <v>136</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="C138" s="5" t="s">
         <v>78</v>
@@ -26436,10 +26247,10 @@
         <v>33158</v>
       </c>
       <c r="F138" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>1081</v>
+        <v>1062</v>
       </c>
       <c r="H138" s="7">
         <v>948529669</v>
@@ -26450,7 +26261,7 @@
         <v>137</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>80</v>
@@ -26462,10 +26273,10 @@
         <v>30256</v>
       </c>
       <c r="F139" s="11" t="s">
-        <v>906</v>
+        <v>887</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>1082</v>
+        <v>1063</v>
       </c>
       <c r="H139" s="12">
         <v>945688198</v>
@@ -26476,7 +26287,7 @@
         <v>138</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>926</v>
+        <v>907</v>
       </c>
       <c r="C140" s="5" t="s">
         <v>129</v>
@@ -26488,10 +26299,10 @@
         <v>31887</v>
       </c>
       <c r="F140" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>1083</v>
+        <v>1064</v>
       </c>
       <c r="H140" s="7">
         <v>941123233</v>
@@ -26502,7 +26313,7 @@
         <v>139</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>926</v>
+        <v>907</v>
       </c>
       <c r="C141" s="5" t="s">
         <v>132</v>
@@ -26514,10 +26325,10 @@
         <v>34495</v>
       </c>
       <c r="F141" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>1084</v>
+        <v>1065</v>
       </c>
       <c r="H141" s="7">
         <v>856020555</v>
@@ -26528,7 +26339,7 @@
         <v>140</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>926</v>
+        <v>907</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>135</v>
@@ -26540,10 +26351,10 @@
         <v>32475</v>
       </c>
       <c r="F142" s="11" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G142" s="8" t="s">
-        <v>1085</v>
+        <v>1066</v>
       </c>
       <c r="H142" s="12">
         <v>819889698</v>
@@ -26554,7 +26365,7 @@
         <v>141</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>926</v>
+        <v>907</v>
       </c>
       <c r="C143" s="5" t="s">
         <v>138</v>
@@ -26566,10 +26377,10 @@
         <v>32770</v>
       </c>
       <c r="F143" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>1086</v>
+        <v>1067</v>
       </c>
       <c r="H143" s="7">
         <v>918793045</v>
@@ -26580,7 +26391,7 @@
         <v>142</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>931</v>
+        <v>912</v>
       </c>
       <c r="C144" s="5" t="s">
         <v>157</v>
@@ -26592,10 +26403,10 @@
         <v>30530</v>
       </c>
       <c r="F144" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>1087</v>
+        <v>1068</v>
       </c>
       <c r="H144" s="7">
         <v>916833223</v>
@@ -26606,7 +26417,7 @@
         <v>143</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>931</v>
+        <v>912</v>
       </c>
       <c r="C145" s="5" t="s">
         <v>160</v>
@@ -26618,10 +26429,10 @@
         <v>31966</v>
       </c>
       <c r="F145" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>1088</v>
+        <v>1069</v>
       </c>
       <c r="H145" s="7">
         <v>912104433</v>
@@ -26632,7 +26443,7 @@
         <v>144</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>931</v>
+        <v>912</v>
       </c>
       <c r="C146" s="5" t="s">
         <v>154</v>
@@ -26644,10 +26455,10 @@
         <v>33221</v>
       </c>
       <c r="F146" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>1089</v>
+        <v>1070</v>
       </c>
       <c r="H146" s="7">
         <v>911312990</v>
@@ -26658,7 +26469,7 @@
         <v>145</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>931</v>
+        <v>912</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>163</v>
@@ -26670,10 +26481,10 @@
         <v>33134</v>
       </c>
       <c r="F147" s="11" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G147" s="8" t="s">
-        <v>1090</v>
+        <v>1071</v>
       </c>
       <c r="H147" s="12">
         <v>911747266</v>
@@ -26684,7 +26495,7 @@
         <v>146</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>939</v>
+        <v>920</v>
       </c>
       <c r="C148" s="5" t="s">
         <v>187</v>
@@ -26696,10 +26507,10 @@
         <v>30622</v>
       </c>
       <c r="F148" s="10" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>1091</v>
+        <v>1072</v>
       </c>
       <c r="H148" s="7">
         <v>849023555</v>
@@ -26710,7 +26521,7 @@
         <v>147</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>939</v>
+        <v>920</v>
       </c>
       <c r="C149" s="5" t="s">
         <v>190</v>
@@ -26722,10 +26533,10 @@
         <v>30550</v>
       </c>
       <c r="F149" s="10" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>1092</v>
+        <v>1073</v>
       </c>
       <c r="H149" s="7">
         <v>816162222</v>
@@ -26736,7 +26547,7 @@
         <v>148</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>939</v>
+        <v>920</v>
       </c>
       <c r="C150" s="8" t="s">
         <v>193</v>
@@ -26748,10 +26559,10 @@
         <v>29672</v>
       </c>
       <c r="F150" s="11" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G150" s="8" t="s">
-        <v>1093</v>
+        <v>1074</v>
       </c>
       <c r="H150" s="12">
         <v>886761981</v>
@@ -26762,7 +26573,7 @@
         <v>149</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>939</v>
+        <v>920</v>
       </c>
       <c r="C151" s="5" t="s">
         <v>196</v>
@@ -26774,10 +26585,10 @@
         <v>30934</v>
       </c>
       <c r="F151" s="10" t="s">
-        <v>906</v>
+        <v>887</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>1094</v>
+        <v>1075</v>
       </c>
       <c r="H151" s="7">
         <v>914899546</v>
@@ -26788,7 +26599,7 @@
         <v>150</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>939</v>
+        <v>920</v>
       </c>
       <c r="C152" s="5" t="s">
         <v>199</v>
@@ -26800,10 +26611,10 @@
         <v>33239</v>
       </c>
       <c r="F152" s="10" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>1095</v>
+        <v>1076</v>
       </c>
       <c r="H152" s="7">
         <v>886581281</v>
@@ -26814,7 +26625,7 @@
         <v>151</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="C153" s="8" t="s">
         <v>226</v>
@@ -26826,10 +26637,10 @@
         <v>31722</v>
       </c>
       <c r="F153" s="11" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G153" s="8" t="s">
-        <v>1096</v>
+        <v>1077</v>
       </c>
       <c r="H153" s="12">
         <v>835155999</v>
@@ -26840,7 +26651,7 @@
         <v>152</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="C154" s="5" t="s">
         <v>229</v>
@@ -26852,10 +26663,10 @@
         <v>32239</v>
       </c>
       <c r="F154" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>1097</v>
+        <v>1078</v>
       </c>
       <c r="H154" s="7">
         <v>917677600</v>
@@ -26866,7 +26677,7 @@
         <v>153</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="C155" s="5" t="s">
         <v>232</v>
@@ -26878,10 +26689,10 @@
         <v>24907</v>
       </c>
       <c r="F155" s="10" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>1098</v>
+        <v>1079</v>
       </c>
       <c r="H155" s="7">
         <v>949239366</v>
@@ -26892,7 +26703,7 @@
         <v>154</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="C156" s="5" t="s">
         <v>235</v>
@@ -26904,10 +26715,10 @@
         <v>26444</v>
       </c>
       <c r="F156" s="10" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>1099</v>
+        <v>1080</v>
       </c>
       <c r="H156" s="7">
         <v>916279727</v>
@@ -26918,7 +26729,7 @@
         <v>155</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="C157" s="5" t="s">
         <v>238</v>
@@ -26930,10 +26741,10 @@
         <v>29492</v>
       </c>
       <c r="F157" s="10" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>1100</v>
+        <v>1081</v>
       </c>
       <c r="H157" s="7">
         <v>914913145</v>
@@ -26944,7 +26755,7 @@
         <v>156</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="C158" s="5" t="s">
         <v>241</v>
@@ -26956,10 +26767,10 @@
         <v>32754</v>
       </c>
       <c r="F158" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>1101</v>
+        <v>1082</v>
       </c>
       <c r="H158" s="7">
         <v>833676186</v>
@@ -26970,7 +26781,7 @@
         <v>157</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="C159" s="8" t="s">
         <v>244</v>
@@ -26982,10 +26793,10 @@
         <v>34163</v>
       </c>
       <c r="F159" s="11" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>1102</v>
+        <v>1083</v>
       </c>
       <c r="H159" s="12">
         <v>833313793</v>
@@ -26996,7 +26807,7 @@
         <v>158</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="C160" s="5" t="s">
         <v>247</v>
@@ -27008,10 +26819,10 @@
         <v>32583</v>
       </c>
       <c r="F160" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>1103</v>
+        <v>1084</v>
       </c>
       <c r="H160" s="7">
         <v>941631989</v>
@@ -27022,7 +26833,7 @@
         <v>159</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="C161" s="5" t="s">
         <v>250</v>
@@ -27034,10 +26845,10 @@
         <v>34157</v>
       </c>
       <c r="F161" s="10" t="s">
-        <v>906</v>
+        <v>887</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>1104</v>
+        <v>1085</v>
       </c>
       <c r="H161" s="7">
         <v>348537004</v>
@@ -27048,7 +26859,7 @@
         <v>160</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="C162" s="5" t="s">
         <v>253</v>
@@ -27060,10 +26871,10 @@
         <v>34695</v>
       </c>
       <c r="F162" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>1105</v>
+        <v>1086</v>
       </c>
       <c r="H162" s="7">
         <v>858332211</v>
@@ -27074,7 +26885,7 @@
         <v>161</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="C163" s="5" t="s">
         <v>256</v>
@@ -27086,10 +26897,10 @@
         <v>33530</v>
       </c>
       <c r="F163" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>1106</v>
+        <v>1087</v>
       </c>
       <c r="H163" s="7">
         <v>846334686</v>
@@ -27100,7 +26911,7 @@
         <v>162</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="C164" s="5" t="s">
         <v>259</v>
@@ -27112,10 +26923,10 @@
         <v>32312</v>
       </c>
       <c r="F164" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>1107</v>
+        <v>1088</v>
       </c>
       <c r="H164" s="7">
         <v>912490102</v>
@@ -27126,7 +26937,7 @@
         <v>163</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>956</v>
+        <v>937</v>
       </c>
       <c r="C165" s="5" t="s">
         <v>280</v>
@@ -27138,10 +26949,10 @@
         <v>32599</v>
       </c>
       <c r="F165" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>1108</v>
+        <v>1089</v>
       </c>
       <c r="H165" s="7">
         <v>914962262</v>
@@ -27152,7 +26963,7 @@
         <v>164</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>956</v>
+        <v>937</v>
       </c>
       <c r="C166" s="5" t="s">
         <v>283</v>
@@ -27164,10 +26975,10 @@
         <v>29330</v>
       </c>
       <c r="F166" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>1109</v>
+        <v>1090</v>
       </c>
       <c r="H166" s="7">
         <v>947450444</v>
@@ -27178,7 +26989,7 @@
         <v>165</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>956</v>
+        <v>937</v>
       </c>
       <c r="C167" s="5" t="s">
         <v>286</v>
@@ -27190,10 +27001,10 @@
         <v>33746</v>
       </c>
       <c r="F167" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>1110</v>
+        <v>1091</v>
       </c>
       <c r="H167" s="7">
         <v>917022592</v>
@@ -27204,7 +27015,7 @@
         <v>166</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>956</v>
+        <v>937</v>
       </c>
       <c r="C168" s="5" t="s">
         <v>289</v>
@@ -27216,10 +27027,10 @@
         <v>32865</v>
       </c>
       <c r="F168" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>1111</v>
+        <v>1092</v>
       </c>
       <c r="H168" s="7">
         <v>829861128</v>
@@ -27230,7 +27041,7 @@
         <v>167</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="C169" s="5" t="s">
         <v>313</v>
@@ -27242,10 +27053,10 @@
         <v>35282</v>
       </c>
       <c r="F169" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>1112</v>
+        <v>1093</v>
       </c>
       <c r="H169" s="7">
         <v>941092376</v>
@@ -27256,7 +27067,7 @@
         <v>168</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="C170" s="5" t="s">
         <v>316</v>
@@ -27268,10 +27079,10 @@
         <v>36880</v>
       </c>
       <c r="F170" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>1113</v>
+        <v>1094</v>
       </c>
       <c r="H170" s="7">
         <v>917600366</v>
@@ -27282,7 +27093,7 @@
         <v>169</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="C171" s="5" t="s">
         <v>319</v>
@@ -27294,10 +27105,10 @@
         <v>31516</v>
       </c>
       <c r="F171" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>1114</v>
+        <v>1095</v>
       </c>
       <c r="H171" s="7">
         <v>949328222</v>
@@ -27308,7 +27119,7 @@
         <v>170</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="C172" s="8" t="s">
         <v>322</v>
@@ -27320,10 +27131,10 @@
         <v>34278</v>
       </c>
       <c r="F172" s="11" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G172" s="8" t="s">
-        <v>1115</v>
+        <v>1096</v>
       </c>
       <c r="H172" s="12">
         <v>835850333</v>
@@ -27334,7 +27145,7 @@
         <v>171</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="C173" s="5" t="s">
         <v>325</v>
@@ -27346,10 +27157,10 @@
         <v>30623</v>
       </c>
       <c r="F173" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>1116</v>
+        <v>1097</v>
       </c>
       <c r="H173" s="7">
         <v>966826781</v>
@@ -27360,7 +27171,7 @@
         <v>172</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="C174" s="5" t="s">
         <v>328</v>
@@ -27372,10 +27183,10 @@
         <v>33133</v>
       </c>
       <c r="F174" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>1117</v>
+        <v>1098</v>
       </c>
       <c r="H174" s="7">
         <v>948617990</v>
@@ -27386,7 +27197,7 @@
         <v>173</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="C175" s="5" t="s">
         <v>331</v>
@@ -27398,10 +27209,10 @@
         <v>31134</v>
       </c>
       <c r="F175" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>1118</v>
+        <v>1099</v>
       </c>
       <c r="H175" s="7">
         <v>816212185</v>
@@ -27412,7 +27223,7 @@
         <v>174</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="C176" s="5" t="s">
         <v>334</v>
@@ -27424,10 +27235,10 @@
         <v>32603</v>
       </c>
       <c r="F176" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>1119</v>
+        <v>1100</v>
       </c>
       <c r="H176" s="7">
         <v>947436389</v>
@@ -27438,7 +27249,7 @@
         <v>175</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>973</v>
+        <v>954</v>
       </c>
       <c r="C177" s="8" t="s">
         <v>361</v>
@@ -27450,10 +27261,10 @@
         <v>34706</v>
       </c>
       <c r="F177" s="11" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G177" s="8" t="s">
-        <v>1120</v>
+        <v>1101</v>
       </c>
       <c r="H177" s="12">
         <v>914333829</v>
@@ -27464,7 +27275,7 @@
         <v>176</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>973</v>
+        <v>954</v>
       </c>
       <c r="C178" s="5" t="s">
         <v>364</v>
@@ -27476,10 +27287,10 @@
         <v>38395</v>
       </c>
       <c r="F178" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G178" s="5" t="s">
-        <v>1121</v>
+        <v>1102</v>
       </c>
       <c r="H178" s="7">
         <v>916456005</v>
@@ -27490,7 +27301,7 @@
         <v>177</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>973</v>
+        <v>954</v>
       </c>
       <c r="C179" s="5" t="s">
         <v>367</v>
@@ -27502,10 +27313,10 @@
         <v>36996</v>
       </c>
       <c r="F179" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>1122</v>
+        <v>1103</v>
       </c>
       <c r="H179" s="7">
         <v>889115401</v>
@@ -27516,7 +27327,7 @@
         <v>178</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>973</v>
+        <v>954</v>
       </c>
       <c r="C180" s="5" t="s">
         <v>369</v>
@@ -27528,10 +27339,10 @@
         <v>31558</v>
       </c>
       <c r="F180" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G180" s="5" t="s">
-        <v>1123</v>
+        <v>1104</v>
       </c>
       <c r="H180" s="7">
         <v>818135205</v>
@@ -27542,7 +27353,7 @@
         <v>179</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>973</v>
+        <v>954</v>
       </c>
       <c r="C181" s="5" t="s">
         <v>372</v>
@@ -27554,10 +27365,10 @@
         <v>34443</v>
       </c>
       <c r="F181" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>1124</v>
+        <v>1105</v>
       </c>
       <c r="H181" s="7">
         <v>836080419</v>
@@ -27568,7 +27379,7 @@
         <v>180</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>973</v>
+        <v>954</v>
       </c>
       <c r="C182" s="5" t="s">
         <v>376</v>
@@ -27580,10 +27391,10 @@
         <v>34359</v>
       </c>
       <c r="F182" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G182" s="5" t="s">
-        <v>1125</v>
+        <v>1106</v>
       </c>
       <c r="H182" s="7">
         <v>835291994</v>
@@ -27594,7 +27405,7 @@
         <v>181</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>973</v>
+        <v>954</v>
       </c>
       <c r="C183" s="5" t="s">
         <v>379</v>
@@ -27606,10 +27417,10 @@
         <v>31677</v>
       </c>
       <c r="F183" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G183" s="5" t="s">
-        <v>1126</v>
+        <v>1107</v>
       </c>
       <c r="H183" s="7">
         <v>825349395</v>
@@ -27620,7 +27431,7 @@
         <v>182</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>973</v>
+        <v>954</v>
       </c>
       <c r="C184" s="5" t="s">
         <v>382</v>
@@ -27632,10 +27443,10 @@
         <v>36500</v>
       </c>
       <c r="F184" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G184" s="5" t="s">
-        <v>1127</v>
+        <v>1108</v>
       </c>
       <c r="H184" s="7">
         <v>834808871</v>
@@ -27646,7 +27457,7 @@
         <v>183</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>973</v>
+        <v>954</v>
       </c>
       <c r="C185" s="5" t="s">
         <v>385</v>
@@ -27658,10 +27469,10 @@
         <v>31093</v>
       </c>
       <c r="F185" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G185" s="5" t="s">
-        <v>1128</v>
+        <v>1109</v>
       </c>
       <c r="H185" s="7">
         <v>912099420</v>
@@ -27672,7 +27483,7 @@
         <v>184</v>
       </c>
       <c r="B186" s="8" t="s">
-        <v>979</v>
+        <v>960</v>
       </c>
       <c r="C186" s="8" t="s">
         <v>406</v>
@@ -27684,10 +27495,10 @@
         <v>33383</v>
       </c>
       <c r="F186" s="11" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G186" s="8" t="s">
-        <v>1129</v>
+        <v>1110</v>
       </c>
       <c r="H186" s="12">
         <v>917936286</v>
@@ -27698,7 +27509,7 @@
         <v>185</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>979</v>
+        <v>960</v>
       </c>
       <c r="C187" s="5" t="s">
         <v>409</v>
@@ -27710,10 +27521,10 @@
         <v>32716</v>
       </c>
       <c r="F187" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G187" s="5" t="s">
-        <v>1130</v>
+        <v>1111</v>
       </c>
       <c r="H187" s="7">
         <v>886133663</v>
@@ -27724,7 +27535,7 @@
         <v>186</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>979</v>
+        <v>960</v>
       </c>
       <c r="C188" s="5" t="s">
         <v>412</v>
@@ -27736,10 +27547,10 @@
         <v>30110</v>
       </c>
       <c r="F188" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G188" s="5" t="s">
-        <v>1131</v>
+        <v>1112</v>
       </c>
       <c r="H188" s="7">
         <v>843068076</v>
@@ -27750,7 +27561,7 @@
         <v>187</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>979</v>
+        <v>960</v>
       </c>
       <c r="C189" s="5" t="s">
         <v>415</v>
@@ -27762,10 +27573,10 @@
         <v>32570</v>
       </c>
       <c r="F189" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>1132</v>
+        <v>1113</v>
       </c>
       <c r="H189" s="7">
         <v>916436123</v>
@@ -27776,7 +27587,7 @@
         <v>188</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
       <c r="C190" s="5" t="s">
         <v>457</v>
@@ -27788,10 +27599,10 @@
         <v>29777</v>
       </c>
       <c r="F190" s="10" t="s">
-        <v>906</v>
+        <v>887</v>
       </c>
       <c r="G190" s="5" t="s">
-        <v>1133</v>
+        <v>1114</v>
       </c>
       <c r="H190" s="7">
         <v>941747630</v>
@@ -27802,7 +27613,7 @@
         <v>189</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
       <c r="C191" s="5" t="s">
         <v>460</v>
@@ -27814,10 +27625,10 @@
         <v>33207</v>
       </c>
       <c r="F191" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G191" s="5" t="s">
-        <v>1134</v>
+        <v>1115</v>
       </c>
       <c r="H191" s="7">
         <v>886190961</v>
@@ -27828,7 +27639,7 @@
         <v>190</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
       <c r="C192" s="5" t="s">
         <v>463</v>
@@ -27840,10 +27651,10 @@
         <v>37415</v>
       </c>
       <c r="F192" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G192" s="5" t="s">
-        <v>1135</v>
+        <v>1116</v>
       </c>
       <c r="H192" s="7">
         <v>943704988</v>
@@ -27854,7 +27665,7 @@
         <v>191</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
       <c r="C193" s="5" t="s">
         <v>466</v>
@@ -27866,10 +27677,10 @@
         <v>31606</v>
       </c>
       <c r="F193" s="10" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G193" s="5" t="s">
-        <v>1136</v>
+        <v>1117</v>
       </c>
       <c r="H193" s="7">
         <v>845885078</v>
@@ -27880,7 +27691,7 @@
         <v>192</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
       <c r="C194" s="5" t="s">
         <v>469</v>
@@ -27892,10 +27703,10 @@
         <v>33284</v>
       </c>
       <c r="F194" s="10" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G194" s="5" t="s">
-        <v>1137</v>
+        <v>1118</v>
       </c>
       <c r="H194" s="7">
         <v>813331991</v>
@@ -27906,7 +27717,7 @@
         <v>193</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
       <c r="C195" s="5" t="s">
         <v>472</v>
@@ -27918,10 +27729,10 @@
         <v>25063</v>
       </c>
       <c r="F195" s="10" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="G195" s="5" t="s">
-        <v>1138</v>
+        <v>1119</v>
       </c>
       <c r="H195" s="7">
         <v>918547379</v>
@@ -27932,7 +27743,7 @@
         <v>194</v>
       </c>
       <c r="B196" s="8" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
       <c r="C196" s="8" t="s">
         <v>475</v>
@@ -27944,10 +27755,10 @@
         <v>36973</v>
       </c>
       <c r="F196" s="11" t="s">
-        <v>906</v>
+        <v>887</v>
       </c>
       <c r="G196" s="8" t="s">
-        <v>1139</v>
+        <v>1120</v>
       </c>
       <c r="H196" s="12">
         <v>886144486</v>
@@ -27958,7 +27769,7 @@
         <v>195</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
       <c r="C197" s="5" t="s">
         <v>478</v>
@@ -27970,10 +27781,10 @@
         <v>32280</v>
       </c>
       <c r="F197" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G197" s="5" t="s">
-        <v>1140</v>
+        <v>1121</v>
       </c>
       <c r="H197" s="7">
         <v>919753029</v>
@@ -27984,7 +27795,7 @@
         <v>196</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
       <c r="C198" s="5" t="s">
         <v>481</v>
@@ -27996,10 +27807,10 @@
         <v>33576</v>
       </c>
       <c r="F198" s="10" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G198" s="5" t="s">
-        <v>1141</v>
+        <v>1122</v>
       </c>
       <c r="H198" s="7">
         <v>917359606</v>
@@ -28010,7 +27821,7 @@
         <v>197</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>1010</v>
+        <v>991</v>
       </c>
       <c r="C199" s="5" t="s">
         <v>511</v>
@@ -28022,10 +27833,10 @@
         <v>30230</v>
       </c>
       <c r="F199" s="10" t="s">
-        <v>1004</v>
+        <v>985</v>
       </c>
       <c r="G199" s="5" t="s">
-        <v>1142</v>
+        <v>1123</v>
       </c>
       <c r="H199" s="7">
         <v>912039246</v>
@@ -28036,7 +27847,7 @@
         <v>198</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>1016</v>
+        <v>997</v>
       </c>
       <c r="C200" s="5" t="s">
         <v>569</v>
@@ -28048,10 +27859,10 @@
         <v>35303</v>
       </c>
       <c r="F200" s="10" t="s">
-        <v>1004</v>
+        <v>985</v>
       </c>
       <c r="G200" s="5" t="s">
-        <v>1143</v>
+        <v>1124</v>
       </c>
       <c r="H200" s="7">
         <v>888068410</v>
@@ -28062,7 +27873,7 @@
         <v>199</v>
       </c>
       <c r="B201" s="13" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C201" s="13" t="s">
         <v>44</v>
@@ -28074,10 +27885,10 @@
         <v>28716</v>
       </c>
       <c r="F201" s="11" t="s">
-        <v>1042</v>
+        <v>1023</v>
       </c>
       <c r="G201" s="13" t="s">
-        <v>1144</v>
+        <v>1125</v>
       </c>
       <c r="H201" s="15">
         <v>911535088</v>
